--- a/task130/target/northcourt_stratification_2026_claims_final.xlsx
+++ b/task130/target/northcourt_stratification_2026_claims_final.xlsx
@@ -16,590 +16,6 @@
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="193">
-  <si>
-    <t>Northcourt Care Partners</t>
-  </si>
-  <si>
-    <t>Clinical Analytics</t>
-  </si>
-  <si>
-    <t>Document</t>
-  </si>
-  <si>
-    <t>Final Enrolment List, Care Management Services Agreement RCV-2027-014, Section 3.2</t>
-  </si>
-  <si>
-    <t>Client</t>
-  </si>
-  <si>
-    <t>Red Cedar Valley Schools Employee Health Plan (ISD 2817)</t>
-  </si>
-  <si>
-    <t>Prepared by</t>
-  </si>
-  <si>
-    <t>Amy Kelley, Clinical Analytics; Allison Santiago, Account Lead</t>
-  </si>
-  <si>
-    <t>Delivered</t>
-  </si>
-  <si>
-    <t>5 March 2027</t>
-  </si>
-  <si>
-    <t>Data basis</t>
-  </si>
-  <si>
-    <t>Ellery medical and Quarrystone pharmacy claims incurred 1 January to 31 December 2026, paid through 28 February 2027; members enrolled on 1 March 2027</t>
-  </si>
-  <si>
-    <t>Member ID</t>
-  </si>
-  <si>
-    <t>Ellery member ID</t>
-  </si>
-  <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>Northcourt Acuity Model 4.2, run on one calendar year of claims</t>
-  </si>
-  <si>
-    <t>Score</t>
-  </si>
-  <si>
-    <t>0 to 100, shown to one decimal; ranks use the unrounded score</t>
-  </si>
-  <si>
-    <t>Selection</t>
-  </si>
-  <si>
-    <t>The 140 highest-scoring members enrolled on 1 March 2027</t>
-  </si>
-  <si>
-    <t>Risk tiers</t>
-  </si>
-  <si>
-    <t>Tier 1: 53.5 and above; Tier 2: 45.5 to 53.4; Tier 3: 40.0 to 45.4; Tier 4: below 40.0</t>
-  </si>
-  <si>
-    <t>Programme Year</t>
-  </si>
-  <si>
-    <t>1 April 2027 to 31 March 2028</t>
-  </si>
-  <si>
-    <t>Supersedes</t>
-  </si>
-  <si>
-    <t>Draft stratification of 14 January 2027</t>
-  </si>
-  <si>
-    <t>Confidential</t>
-  </si>
-  <si>
-    <t>Contains protected health information.</t>
-  </si>
-  <si>
-    <t>Rank</t>
-  </si>
-  <si>
-    <t>Relationship</t>
-  </si>
-  <si>
-    <t>Date of birth</t>
-  </si>
-  <si>
-    <t>Sex</t>
-  </si>
-  <si>
-    <t>Acuity score</t>
-  </si>
-  <si>
-    <t>Risk tier</t>
-  </si>
-  <si>
-    <t>Care team</t>
-  </si>
-  <si>
-    <t>Enrolment effective</t>
-  </si>
-  <si>
-    <t>RCV2162623</t>
-  </si>
-  <si>
-    <t>Subscriber</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>RN Team A</t>
-  </si>
-  <si>
-    <t>RCV2052974</t>
-  </si>
-  <si>
-    <t>Spouse</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>RN Team B</t>
-  </si>
-  <si>
-    <t>RCV2449840</t>
-  </si>
-  <si>
-    <t>RN Team C</t>
-  </si>
-  <si>
-    <t>RCV1471527</t>
-  </si>
-  <si>
-    <t>RCV8664303</t>
-  </si>
-  <si>
-    <t>RCV7985309</t>
-  </si>
-  <si>
-    <t>RCV3486095</t>
-  </si>
-  <si>
-    <t>RCV4853885</t>
-  </si>
-  <si>
-    <t>RCV4984624</t>
-  </si>
-  <si>
-    <t>RCV6709117</t>
-  </si>
-  <si>
-    <t>RCV5002163</t>
-  </si>
-  <si>
-    <t>RCV2793750</t>
-  </si>
-  <si>
-    <t>RCV5033358</t>
-  </si>
-  <si>
-    <t>RCV3270069</t>
-  </si>
-  <si>
-    <t>RCV8113015</t>
-  </si>
-  <si>
-    <t>Dependent</t>
-  </si>
-  <si>
-    <t>RCV2071330</t>
-  </si>
-  <si>
-    <t>RCV9004175</t>
-  </si>
-  <si>
-    <t>RCV6109161</t>
-  </si>
-  <si>
-    <t>RCV3675980</t>
-  </si>
-  <si>
-    <t>RCV6942976</t>
-  </si>
-  <si>
-    <t>RCV3384885</t>
-  </si>
-  <si>
-    <t>RCV6852162</t>
-  </si>
-  <si>
-    <t>RCV2093187</t>
-  </si>
-  <si>
-    <t>RCV2986773</t>
-  </si>
-  <si>
-    <t>RCV3988147</t>
-  </si>
-  <si>
-    <t>RCV4025966</t>
-  </si>
-  <si>
-    <t>RCV2034883</t>
-  </si>
-  <si>
-    <t>RCV5848032</t>
-  </si>
-  <si>
-    <t>RCV3257800</t>
-  </si>
-  <si>
-    <t>RCV1631184</t>
-  </si>
-  <si>
-    <t>RCV5817074</t>
-  </si>
-  <si>
-    <t>RCV6252913</t>
-  </si>
-  <si>
-    <t>RCV7732575</t>
-  </si>
-  <si>
-    <t>RCV8201043</t>
-  </si>
-  <si>
-    <t>RCV3354070</t>
-  </si>
-  <si>
-    <t>RCV4446063</t>
-  </si>
-  <si>
-    <t>RCV8039901</t>
-  </si>
-  <si>
-    <t>RCV9604944</t>
-  </si>
-  <si>
-    <t>RCV8201650</t>
-  </si>
-  <si>
-    <t>RCV7790956</t>
-  </si>
-  <si>
-    <t>RCV9720871</t>
-  </si>
-  <si>
-    <t>RCV1696191</t>
-  </si>
-  <si>
-    <t>RCV3920778</t>
-  </si>
-  <si>
-    <t>RCV2684889</t>
-  </si>
-  <si>
-    <t>RCV4697258</t>
-  </si>
-  <si>
-    <t>RCV3496532</t>
-  </si>
-  <si>
-    <t>RCV2337518</t>
-  </si>
-  <si>
-    <t>RCV3350408</t>
-  </si>
-  <si>
-    <t>RCV9680142</t>
-  </si>
-  <si>
-    <t>RCV9804176</t>
-  </si>
-  <si>
-    <t>RCV3674913</t>
-  </si>
-  <si>
-    <t>RCV2806970</t>
-  </si>
-  <si>
-    <t>RCV1895300</t>
-  </si>
-  <si>
-    <t>RCV5105634</t>
-  </si>
-  <si>
-    <t>RCV8017643</t>
-  </si>
-  <si>
-    <t>Health Coach Team 1</t>
-  </si>
-  <si>
-    <t>RCV1382141</t>
-  </si>
-  <si>
-    <t>Health Coach Team 2</t>
-  </si>
-  <si>
-    <t>RCV1259489</t>
-  </si>
-  <si>
-    <t>RCV8515349</t>
-  </si>
-  <si>
-    <t>RCV2636159</t>
-  </si>
-  <si>
-    <t>RCV4971588</t>
-  </si>
-  <si>
-    <t>RCV5561802</t>
-  </si>
-  <si>
-    <t>RCV8533759</t>
-  </si>
-  <si>
-    <t>RCV2881382</t>
-  </si>
-  <si>
-    <t>RCV9611207</t>
-  </si>
-  <si>
-    <t>RCV6205499</t>
-  </si>
-  <si>
-    <t>RCV4617151</t>
-  </si>
-  <si>
-    <t>RCV3504511</t>
-  </si>
-  <si>
-    <t>RCV1272289</t>
-  </si>
-  <si>
-    <t>RCV8711464</t>
-  </si>
-  <si>
-    <t>RCV9942243</t>
-  </si>
-  <si>
-    <t>RCV6485110</t>
-  </si>
-  <si>
-    <t>RCV3374758</t>
-  </si>
-  <si>
-    <t>RCV1193295</t>
-  </si>
-  <si>
-    <t>RCV3048005</t>
-  </si>
-  <si>
-    <t>RCV8955620</t>
-  </si>
-  <si>
-    <t>RCV6887720</t>
-  </si>
-  <si>
-    <t>RCV6699713</t>
-  </si>
-  <si>
-    <t>RCV1609805</t>
-  </si>
-  <si>
-    <t>RCV4639248</t>
-  </si>
-  <si>
-    <t>RCV5881068</t>
-  </si>
-  <si>
-    <t>RCV1496883</t>
-  </si>
-  <si>
-    <t>RCV4679176</t>
-  </si>
-  <si>
-    <t>RCV8241336</t>
-  </si>
-  <si>
-    <t>RCV4447334</t>
-  </si>
-  <si>
-    <t>RCV6621103</t>
-  </si>
-  <si>
-    <t>RCV4833002</t>
-  </si>
-  <si>
-    <t>RCV1540781</t>
-  </si>
-  <si>
-    <t>RCV4372242</t>
-  </si>
-  <si>
-    <t>RCV1411588</t>
-  </si>
-  <si>
-    <t>RCV9858043</t>
-  </si>
-  <si>
-    <t>RCV7169467</t>
-  </si>
-  <si>
-    <t>RCV2987476</t>
-  </si>
-  <si>
-    <t>RCV7620380</t>
-  </si>
-  <si>
-    <t>RCV4578207</t>
-  </si>
-  <si>
-    <t>RCV4384005</t>
-  </si>
-  <si>
-    <t>RCV6463574</t>
-  </si>
-  <si>
-    <t>RCV1129734</t>
-  </si>
-  <si>
-    <t>RCV2239641</t>
-  </si>
-  <si>
-    <t>RCV5823710</t>
-  </si>
-  <si>
-    <t>RCV7609755</t>
-  </si>
-  <si>
-    <t>RCV5670618</t>
-  </si>
-  <si>
-    <t>RCV7784552</t>
-  </si>
-  <si>
-    <t>RCV3645671</t>
-  </si>
-  <si>
-    <t>RCV7258375</t>
-  </si>
-  <si>
-    <t>RCV2219400</t>
-  </si>
-  <si>
-    <t>RCV6298861</t>
-  </si>
-  <si>
-    <t>RCV5349249</t>
-  </si>
-  <si>
-    <t>RCV9211395</t>
-  </si>
-  <si>
-    <t>RCV7501192</t>
-  </si>
-  <si>
-    <t>RCV4087111</t>
-  </si>
-  <si>
-    <t>RCV9270534</t>
-  </si>
-  <si>
-    <t>RCV5742338</t>
-  </si>
-  <si>
-    <t>RCV8204209</t>
-  </si>
-  <si>
-    <t>RCV6212770</t>
-  </si>
-  <si>
-    <t>RCV3161342</t>
-  </si>
-  <si>
-    <t>RCV8061593</t>
-  </si>
-  <si>
-    <t>RCV1465607</t>
-  </si>
-  <si>
-    <t>RCV6179969</t>
-  </si>
-  <si>
-    <t>RCV1033212</t>
-  </si>
-  <si>
-    <t>RCV4353887</t>
-  </si>
-  <si>
-    <t>RCV1034053</t>
-  </si>
-  <si>
-    <t>RCV7496703</t>
-  </si>
-  <si>
-    <t>RCV8253398</t>
-  </si>
-  <si>
-    <t>RCV4553312</t>
-  </si>
-  <si>
-    <t>RCV8954786</t>
-  </si>
-  <si>
-    <t>RCV1798738</t>
-  </si>
-  <si>
-    <t>RCV3641827</t>
-  </si>
-  <si>
-    <t>RCV9768130</t>
-  </si>
-  <si>
-    <t>RCV1932981</t>
-  </si>
-  <si>
-    <t>RCV1692281</t>
-  </si>
-  <si>
-    <t>RCV8564895</t>
-  </si>
-  <si>
-    <t>RCV6201973</t>
-  </si>
-  <si>
-    <t>RCV3459745</t>
-  </si>
-  <si>
-    <t>RCV8534707</t>
-  </si>
-  <si>
-    <t>RCV8440739</t>
-  </si>
-  <si>
-    <t>RCV1698430</t>
-  </si>
-  <si>
-    <t>RCV6275373</t>
-  </si>
-  <si>
-    <t>RCV9354537</t>
-  </si>
-  <si>
-    <t>RCV7430793</t>
-  </si>
-  <si>
-    <t>RCV1834252</t>
-  </si>
-  <si>
-    <t>Score range</t>
-  </si>
-  <si>
-    <t>Members</t>
-  </si>
-  <si>
-    <t>53.5 and above</t>
-  </si>
-  <si>
-    <t>45.5 to 53.4</t>
-  </si>
-  <si>
-    <t>40.0 to 45.4</t>
-  </si>
-  <si>
-    <t>below 40.0</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1044,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1052,119 +468,187 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Northcourt Care Partners</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Analytics</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Final Enrolment List, Care Management Services Agreement RCV-2027-014, Section 3.2</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Red Cedar Valley Schools Employee Health Plan (ISD 2817)</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Prepared by</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Amy Kelley, Clinical Analytics; Allison Santiago, Account Lead</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>5 March 2027</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>11</v>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Data basis</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Ellery medical and Quarrystone pharmacy claims incurred 1 January to 31 December 2026, paid through 28 February 2027; members enrolled on 1 March 2027</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>13</v>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Member ID</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Ellery member ID</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>15</v>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Northcourt Acuity Model 4.2, run on one calendar year of claims</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>17</v>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>0 to 100, shown to one decimal; ranks use the unrounded score</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>19</v>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Selection</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>The 140 highest-scoring members enrolled on 1 March 2027</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>21</v>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Risk tiers</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Tier 1: 42.2 and above; Tier 2: 37.9 to 42.1; Tier 3: 35.7 to 37.8; Tier 4: below 35.7</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>23</v>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Programme Year</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>1 April 2027 to 31 March 2028</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>25</v>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Care team</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Assigned under section 4 of the implementation plan</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n"/>
-      <c r="B14" s="2" t="n"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Supersedes</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Draft stratification of 14 January 2027</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>27</v>
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Confidential</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Contains protected health information.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1193,58 +677,84 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>35</v>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Member ID</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Date of birth</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Acuity score</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Risk tier</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Care team</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Enrolment effective</t>
+        </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" t="s">
-        <v>37</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RCV2730530</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>28112</v>
-      </c>
-      <c r="E2" t="s">
-        <v>38</v>
+        <v>27163</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F2" s="6" t="n">
-        <v>63.7</v>
+        <v>66</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="s">
-        <v>39</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>RN Team A</t>
+        </is>
       </c>
       <c r="I2" s="5" t="n">
         <v>46478</v>
@@ -1254,26 +764,34 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" t="s">
-        <v>41</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RCV2123575</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>35385</v>
-      </c>
-      <c r="E3" t="s">
-        <v>42</v>
+        <v>28572</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F3" s="6" t="n">
-        <v>63.5</v>
+        <v>56.1</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="s">
-        <v>43</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>RN Team A</t>
+        </is>
       </c>
       <c r="I3" s="5" t="n">
         <v>46478</v>
@@ -1283,26 +801,34 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RCV7613430</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>30724</v>
-      </c>
-      <c r="E4" t="s">
-        <v>38</v>
+        <v>28314</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F4" s="6" t="n">
-        <v>63.2</v>
+        <v>53.5</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="s">
-        <v>45</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>RN Team A</t>
+        </is>
       </c>
       <c r="I4" s="5" t="n">
         <v>46478</v>
@@ -1312,26 +838,34 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>RCV8695211</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>29828</v>
-      </c>
-      <c r="E5" t="s">
-        <v>38</v>
+        <v>25047</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F5" s="6" t="n">
-        <v>62.6</v>
+        <v>52.1</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="s">
-        <v>39</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>RN Team A</t>
+        </is>
       </c>
       <c r="I5" s="5" t="n">
         <v>46478</v>
@@ -1341,26 +875,34 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>RCV5104636</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>26578</v>
-      </c>
-      <c r="E6" t="s">
-        <v>38</v>
+        <v>25816</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>60.2</v>
+        <v>51.9</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="s">
-        <v>43</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>RN Team A</t>
+        </is>
       </c>
       <c r="I6" s="5" t="n">
         <v>46478</v>
@@ -1370,26 +912,34 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RCV8921118</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>25337</v>
-      </c>
-      <c r="E7" t="s">
-        <v>42</v>
+        <v>29398</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>60.1</v>
+        <v>50.7</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="s">
-        <v>45</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>RN Team A</t>
+        </is>
       </c>
       <c r="I7" s="5" t="n">
         <v>46478</v>
@@ -1399,26 +949,34 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" t="s">
-        <v>41</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RCV5999974</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>24250</v>
-      </c>
-      <c r="E8" t="s">
-        <v>42</v>
+        <v>25712</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>59.1</v>
+        <v>50.2</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="s">
-        <v>39</v>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>RN Team A</t>
+        </is>
       </c>
       <c r="I8" s="5" t="n">
         <v>46478</v>
@@ -1428,26 +986,34 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" t="s">
-        <v>41</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>RCV5529192</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>23401</v>
-      </c>
-      <c r="E9" t="s">
-        <v>42</v>
+        <v>23029</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>58.7</v>
+        <v>49.5</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="s">
-        <v>43</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I9" s="5" t="n">
         <v>46478</v>
@@ -1457,26 +1023,34 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>RCV4142981</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>25659</v>
-      </c>
-      <c r="E10" t="s">
-        <v>38</v>
+        <v>25342</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>57.9</v>
+        <v>48.7</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
-      <c r="H10" t="s">
-        <v>45</v>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>RN Team A</t>
+        </is>
       </c>
       <c r="I10" s="5" t="n">
         <v>46478</v>
@@ -1486,26 +1060,34 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" t="s">
-        <v>41</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>RCV6367920</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>29468</v>
-      </c>
-      <c r="E11" t="s">
-        <v>42</v>
+        <v>24140</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>56.9</v>
+        <v>47.9</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="s">
-        <v>39</v>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>RN Team B</t>
+        </is>
       </c>
       <c r="I11" s="5" t="n">
         <v>46478</v>
@@ -1515,26 +1097,34 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>RCV3449444</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>23650</v>
-      </c>
-      <c r="E12" t="s">
-        <v>38</v>
+        <v>26580</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>56.4</v>
+        <v>47.2</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" t="s">
-        <v>43</v>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>RN Team B</t>
+        </is>
       </c>
       <c r="I12" s="5" t="n">
         <v>46478</v>
@@ -1544,26 +1134,34 @@
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" t="s">
-        <v>41</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>RCV4660775</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>28514</v>
-      </c>
-      <c r="E13" t="s">
-        <v>42</v>
+        <v>27309</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>56</v>
+        <v>46.8</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
-      <c r="H13" t="s">
-        <v>45</v>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>RN Team B</t>
+        </is>
       </c>
       <c r="I13" s="5" t="n">
         <v>46478</v>
@@ -1573,26 +1171,34 @@
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>RCV5035018</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>22013</v>
-      </c>
-      <c r="E14" t="s">
-        <v>42</v>
+        <v>38557</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>55.8</v>
+        <v>46.8</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
-      <c r="H14" t="s">
-        <v>39</v>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I14" s="5" t="n">
         <v>46478</v>
@@ -1602,26 +1208,34 @@
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" t="s">
-        <v>37</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>RCV6528985</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>28481</v>
-      </c>
-      <c r="E15" t="s">
-        <v>38</v>
+        <v>25730</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>55.7</v>
+        <v>46.6</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
-      <c r="H15" t="s">
-        <v>43</v>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I15" s="5" t="n">
         <v>46478</v>
@@ -1631,26 +1245,34 @@
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" t="s">
-        <v>58</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>RCV5816729</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>46141</v>
-      </c>
-      <c r="E16" t="s">
-        <v>42</v>
+        <v>26908</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>55.5</v>
+        <v>46.4</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
-      <c r="H16" t="s">
-        <v>45</v>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I16" s="5" t="n">
         <v>46478</v>
@@ -1660,26 +1282,34 @@
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17" t="s">
-        <v>37</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>RCV1135609</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>36138</v>
-      </c>
-      <c r="E17" t="s">
-        <v>38</v>
+        <v>23369</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>55.2</v>
+        <v>46.1</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
-      <c r="H17" t="s">
-        <v>39</v>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>RN Team B</t>
+        </is>
       </c>
       <c r="I17" s="5" t="n">
         <v>46478</v>
@@ -1689,26 +1319,34 @@
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18" t="s">
-        <v>37</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>RCV8355110</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>27709</v>
-      </c>
-      <c r="E18" t="s">
-        <v>38</v>
+        <v>22295</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>54.2</v>
+        <v>45.9</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
-      <c r="H18" t="s">
-        <v>43</v>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>RN Team A</t>
+        </is>
       </c>
       <c r="I18" s="5" t="n">
         <v>46478</v>
@@ -1718,26 +1356,34 @@
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" t="s">
-        <v>37</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>RCV8692544</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>33797</v>
-      </c>
-      <c r="E19" t="s">
-        <v>42</v>
+        <v>24122</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>53.9</v>
+        <v>45.7</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
-      <c r="H19" t="s">
-        <v>45</v>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I19" s="5" t="n">
         <v>46478</v>
@@ -1747,26 +1393,34 @@
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" t="s">
-        <v>37</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>RCV9467205</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>27942</v>
-      </c>
-      <c r="E20" t="s">
-        <v>42</v>
+        <v>24582</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>53.7</v>
+        <v>45.7</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
-      <c r="H20" t="s">
-        <v>39</v>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>RN Team B</t>
+        </is>
       </c>
       <c r="I20" s="5" t="n">
         <v>46478</v>
@@ -1776,26 +1430,34 @@
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" t="s">
-        <v>41</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>RCV7885533</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>21946</v>
-      </c>
-      <c r="E21" t="s">
-        <v>42</v>
+        <v>26975</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>53.6</v>
+        <v>45.5</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
-      <c r="H21" t="s">
-        <v>43</v>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>RN Team B</t>
+        </is>
       </c>
       <c r="I21" s="5" t="n">
         <v>46478</v>
@@ -1805,26 +1467,34 @@
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" t="s">
-        <v>41</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>RCV4189407</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>22733</v>
-      </c>
-      <c r="E22" t="s">
-        <v>42</v>
+        <v>29800</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>53.4</v>
+        <v>45.5</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
-      </c>
-      <c r="H22" t="s">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>RN Team B</t>
+        </is>
       </c>
       <c r="I22" s="5" t="n">
         <v>46478</v>
@@ -1834,26 +1504,34 @@
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" t="s">
-        <v>37</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>RCV1603872</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>23158</v>
-      </c>
-      <c r="E23" t="s">
-        <v>38</v>
+        <v>35090</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>52.9</v>
+        <v>45.3</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" t="s">
-        <v>39</v>
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I23" s="5" t="n">
         <v>46478</v>
@@ -1863,26 +1541,34 @@
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" t="s">
-        <v>37</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>RCV9255613</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>30797</v>
-      </c>
-      <c r="E24" t="s">
-        <v>42</v>
+        <v>26377</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>52.8</v>
+        <v>44.8</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>RN Team A</t>
+        </is>
       </c>
       <c r="I24" s="5" t="n">
         <v>46478</v>
@@ -1892,26 +1578,34 @@
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" t="s">
-        <v>41</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>RCV6227172</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>29539</v>
-      </c>
-      <c r="E25" t="s">
-        <v>42</v>
+        <v>42371</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>52.7</v>
+        <v>44.8</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
-      </c>
-      <c r="H25" t="s">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I25" s="5" t="n">
         <v>46478</v>
@@ -1921,26 +1615,34 @@
       <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" t="s">
-        <v>41</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>RCV2751065</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>28221</v>
-      </c>
-      <c r="E26" t="s">
-        <v>38</v>
+        <v>24692</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>52.5</v>
+        <v>44.5</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" t="s">
-        <v>39</v>
+        <v>1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>RN Team A</t>
+        </is>
       </c>
       <c r="I26" s="5" t="n">
         <v>46478</v>
@@ -1950,26 +1652,34 @@
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" t="s">
-        <v>37</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>RCV3082787</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>36686</v>
-      </c>
-      <c r="E27" t="s">
-        <v>38</v>
+        <v>27148</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>52.4</v>
+        <v>43.8</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
-      </c>
-      <c r="H27" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>RN Team A</t>
+        </is>
       </c>
       <c r="I27" s="5" t="n">
         <v>46478</v>
@@ -1979,26 +1689,34 @@
       <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" t="s">
-        <v>41</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>RCV5995844</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>23571</v>
-      </c>
-      <c r="E28" t="s">
-        <v>42</v>
+        <v>21605</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>51.9</v>
+        <v>43.7</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
-      </c>
-      <c r="H28" t="s">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I28" s="5" t="n">
         <v>46478</v>
@@ -2008,26 +1726,34 @@
       <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29" t="s">
-        <v>41</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>RCV4587185</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>25399</v>
-      </c>
-      <c r="E29" t="s">
-        <v>42</v>
+        <v>24894</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>51.7</v>
+        <v>43.6</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" t="s">
-        <v>39</v>
+        <v>1</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>RN Team B</t>
+        </is>
       </c>
       <c r="I29" s="5" t="n">
         <v>46478</v>
@@ -2037,26 +1763,34 @@
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
-        <v>72</v>
-      </c>
-      <c r="C30" t="s">
-        <v>37</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>RCV9304806</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>27357</v>
-      </c>
-      <c r="E30" t="s">
-        <v>42</v>
+        <v>24622</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>51.2</v>
+        <v>43.1</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I30" s="5" t="n">
         <v>46478</v>
@@ -2066,26 +1800,34 @@
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
-        <v>73</v>
-      </c>
-      <c r="C31" t="s">
-        <v>37</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>RCV8608275</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>26740</v>
-      </c>
-      <c r="E31" t="s">
-        <v>38</v>
+        <v>31641</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>50.7</v>
+        <v>43</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
-      </c>
-      <c r="H31" t="s">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I31" s="5" t="n">
         <v>46478</v>
@@ -2095,26 +1837,34 @@
       <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
-        <v>74</v>
-      </c>
-      <c r="C32" t="s">
-        <v>41</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>RCV8509472</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>23290</v>
-      </c>
-      <c r="E32" t="s">
-        <v>42</v>
+        <v>27468</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>50.6</v>
+        <v>42.7</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
-      </c>
-      <c r="H32" t="s">
-        <v>39</v>
+        <v>1</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>RN Team B</t>
+        </is>
       </c>
       <c r="I32" s="5" t="n">
         <v>46478</v>
@@ -2124,26 +1874,34 @@
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
-        <v>75</v>
-      </c>
-      <c r="C33" t="s">
-        <v>41</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>RCV7426097</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>33488</v>
-      </c>
-      <c r="E33" t="s">
-        <v>38</v>
+        <v>46345</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>50.5</v>
+        <v>42.7</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
-      </c>
-      <c r="H33" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I33" s="5" t="n">
         <v>46478</v>
@@ -2153,26 +1911,34 @@
       <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
-        <v>76</v>
-      </c>
-      <c r="C34" t="s">
-        <v>58</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>RCV1049263</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>39361</v>
-      </c>
-      <c r="E34" t="s">
-        <v>38</v>
+        <v>32024</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>50.2</v>
+        <v>42.7</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
-      </c>
-      <c r="H34" t="s">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>RN Team B</t>
+        </is>
       </c>
       <c r="I34" s="5" t="n">
         <v>46478</v>
@@ -2182,26 +1948,34 @@
       <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
-        <v>77</v>
-      </c>
-      <c r="C35" t="s">
-        <v>41</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>RCV7157512</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>27792</v>
-      </c>
-      <c r="E35" t="s">
-        <v>42</v>
+        <v>23754</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>50.2</v>
+        <v>42.7</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
-      </c>
-      <c r="H35" t="s">
-        <v>39</v>
+        <v>1</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I35" s="5" t="n">
         <v>46478</v>
@@ -2211,26 +1985,34 @@
       <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
-        <v>78</v>
-      </c>
-      <c r="C36" t="s">
-        <v>58</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>RCV6938522</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>46224</v>
-      </c>
-      <c r="E36" t="s">
-        <v>42</v>
+        <v>25222</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>50.1</v>
+        <v>42.3</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
-      </c>
-      <c r="H36" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>RN Team A</t>
+        </is>
       </c>
       <c r="I36" s="5" t="n">
         <v>46478</v>
@@ -2240,26 +2022,34 @@
       <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
-        <v>79</v>
-      </c>
-      <c r="C37" t="s">
-        <v>41</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>RCV4201512</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>26490</v>
-      </c>
-      <c r="E37" t="s">
-        <v>38</v>
+        <v>29300</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>49.2</v>
+        <v>42</v>
       </c>
       <c r="G37" t="n">
         <v>2</v>
       </c>
-      <c r="H37" t="s">
-        <v>45</v>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I37" s="5" t="n">
         <v>46478</v>
@@ -2269,26 +2059,34 @@
       <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
-        <v>80</v>
-      </c>
-      <c r="C38" t="s">
-        <v>37</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>RCV1855123</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>23303</v>
-      </c>
-      <c r="E38" t="s">
-        <v>38</v>
+        <v>32038</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>49.1</v>
+        <v>41.5</v>
       </c>
       <c r="G38" t="n">
         <v>2</v>
       </c>
-      <c r="H38" t="s">
-        <v>39</v>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I38" s="5" t="n">
         <v>46478</v>
@@ -2298,26 +2096,34 @@
       <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
-        <v>81</v>
-      </c>
-      <c r="C39" t="s">
-        <v>37</v>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>RCV3713263</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>26073</v>
-      </c>
-      <c r="E39" t="s">
-        <v>38</v>
+        <v>29087</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>48.6</v>
+        <v>41.4</v>
       </c>
       <c r="G39" t="n">
         <v>2</v>
       </c>
-      <c r="H39" t="s">
-        <v>43</v>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>RN Team B</t>
+        </is>
       </c>
       <c r="I39" s="5" t="n">
         <v>46478</v>
@@ -2327,26 +2133,34 @@
       <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
-        <v>82</v>
-      </c>
-      <c r="C40" t="s">
-        <v>41</v>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>RCV5579448</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>24021</v>
-      </c>
-      <c r="E40" t="s">
-        <v>38</v>
+        <v>25764</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>48.6</v>
+        <v>41.4</v>
       </c>
       <c r="G40" t="n">
         <v>2</v>
       </c>
-      <c r="H40" t="s">
-        <v>45</v>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I40" s="5" t="n">
         <v>46478</v>
@@ -2356,26 +2170,34 @@
       <c r="A41" t="n">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
-        <v>83</v>
-      </c>
-      <c r="C41" t="s">
-        <v>37</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>RCV5181969</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>29081</v>
-      </c>
-      <c r="E41" t="s">
-        <v>42</v>
+        <v>23566</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>48.3</v>
+        <v>40.9</v>
       </c>
       <c r="G41" t="n">
         <v>2</v>
       </c>
-      <c r="H41" t="s">
-        <v>39</v>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>RN Team A</t>
+        </is>
       </c>
       <c r="I41" s="5" t="n">
         <v>46478</v>
@@ -2385,26 +2207,34 @@
       <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
-        <v>84</v>
-      </c>
-      <c r="C42" t="s">
-        <v>58</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>RCV5078746</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>43864</v>
-      </c>
-      <c r="E42" t="s">
-        <v>42</v>
+        <v>28655</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>47.9</v>
+        <v>40.9</v>
       </c>
       <c r="G42" t="n">
         <v>2</v>
       </c>
-      <c r="H42" t="s">
-        <v>43</v>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>RN Team B</t>
+        </is>
       </c>
       <c r="I42" s="5" t="n">
         <v>46478</v>
@@ -2414,26 +2244,34 @@
       <c r="A43" t="n">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
-        <v>85</v>
-      </c>
-      <c r="C43" t="s">
-        <v>37</v>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>RCV5824630</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>23537</v>
-      </c>
-      <c r="E43" t="s">
-        <v>38</v>
+        <v>28492</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>47.9</v>
+        <v>40.8</v>
       </c>
       <c r="G43" t="n">
         <v>2</v>
       </c>
-      <c r="H43" t="s">
-        <v>45</v>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>RN Team A</t>
+        </is>
       </c>
       <c r="I43" s="5" t="n">
         <v>46478</v>
@@ -2443,26 +2281,34 @@
       <c r="A44" t="n">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
-        <v>86</v>
-      </c>
-      <c r="C44" t="s">
-        <v>37</v>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>RCV1070060</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>28013</v>
-      </c>
-      <c r="E44" t="s">
-        <v>38</v>
+        <v>30349</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>47.7</v>
+        <v>40.8</v>
       </c>
       <c r="G44" t="n">
         <v>2</v>
       </c>
-      <c r="H44" t="s">
-        <v>39</v>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I44" s="5" t="n">
         <v>46478</v>
@@ -2472,26 +2318,34 @@
       <c r="A45" t="n">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
-        <v>87</v>
-      </c>
-      <c r="C45" t="s">
-        <v>37</v>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>RCV6875151</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>23830</v>
-      </c>
-      <c r="E45" t="s">
-        <v>38</v>
+        <v>40112</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>47.6</v>
+        <v>40.8</v>
       </c>
       <c r="G45" t="n">
         <v>2</v>
       </c>
-      <c r="H45" t="s">
-        <v>43</v>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I45" s="5" t="n">
         <v>46478</v>
@@ -2501,26 +2355,34 @@
       <c r="A46" t="n">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
-        <v>88</v>
-      </c>
-      <c r="C46" t="s">
-        <v>37</v>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>RCV2327923</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>29706</v>
-      </c>
-      <c r="E46" t="s">
-        <v>42</v>
+        <v>25183</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>47.3</v>
+        <v>40.8</v>
       </c>
       <c r="G46" t="n">
         <v>2</v>
       </c>
-      <c r="H46" t="s">
-        <v>45</v>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>RN Team B</t>
+        </is>
       </c>
       <c r="I46" s="5" t="n">
         <v>46478</v>
@@ -2530,26 +2392,34 @@
       <c r="A47" t="n">
         <v>46</v>
       </c>
-      <c r="B47" t="s">
-        <v>89</v>
-      </c>
-      <c r="C47" t="s">
-        <v>37</v>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>RCV6795042</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>34028</v>
-      </c>
-      <c r="E47" t="s">
-        <v>38</v>
+        <v>23652</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>47.2</v>
+        <v>40.8</v>
       </c>
       <c r="G47" t="n">
         <v>2</v>
       </c>
-      <c r="H47" t="s">
-        <v>39</v>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>RN Team B</t>
+        </is>
       </c>
       <c r="I47" s="5" t="n">
         <v>46478</v>
@@ -2559,26 +2429,34 @@
       <c r="A48" t="n">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
-        <v>90</v>
-      </c>
-      <c r="C48" t="s">
-        <v>41</v>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>RCV8852933</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>23339</v>
-      </c>
-      <c r="E48" t="s">
-        <v>42</v>
+        <v>26254</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>46.8</v>
+        <v>40.6</v>
       </c>
       <c r="G48" t="n">
         <v>2</v>
       </c>
-      <c r="H48" t="s">
-        <v>43</v>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I48" s="5" t="n">
         <v>46478</v>
@@ -2588,26 +2466,34 @@
       <c r="A49" t="n">
         <v>48</v>
       </c>
-      <c r="B49" t="s">
-        <v>91</v>
-      </c>
-      <c r="C49" t="s">
-        <v>37</v>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>RCV2365593</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>24902</v>
-      </c>
-      <c r="E49" t="s">
-        <v>42</v>
+        <v>33612</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>46.5</v>
+        <v>40.4</v>
       </c>
       <c r="G49" t="n">
         <v>2</v>
       </c>
-      <c r="H49" t="s">
-        <v>45</v>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I49" s="5" t="n">
         <v>46478</v>
@@ -2617,26 +2503,34 @@
       <c r="A50" t="n">
         <v>49</v>
       </c>
-      <c r="B50" t="s">
-        <v>92</v>
-      </c>
-      <c r="C50" t="s">
-        <v>37</v>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>RCV3282444</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>28769</v>
-      </c>
-      <c r="E50" t="s">
-        <v>38</v>
+        <v>34034</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>46.4</v>
+        <v>40.1</v>
       </c>
       <c r="G50" t="n">
         <v>2</v>
       </c>
-      <c r="H50" t="s">
-        <v>39</v>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I50" s="5" t="n">
         <v>46478</v>
@@ -2646,26 +2540,34 @@
       <c r="A51" t="n">
         <v>50</v>
       </c>
-      <c r="B51" t="s">
-        <v>93</v>
-      </c>
-      <c r="C51" t="s">
-        <v>37</v>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>RCV8050854</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>23900</v>
-      </c>
-      <c r="E51" t="s">
-        <v>38</v>
+        <v>24862</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>46.3</v>
+        <v>40</v>
       </c>
       <c r="G51" t="n">
         <v>2</v>
       </c>
-      <c r="H51" t="s">
-        <v>43</v>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>RN Team B</t>
+        </is>
       </c>
       <c r="I51" s="5" t="n">
         <v>46478</v>
@@ -2675,26 +2577,34 @@
       <c r="A52" t="n">
         <v>51</v>
       </c>
-      <c r="B52" t="s">
-        <v>94</v>
-      </c>
-      <c r="C52" t="s">
-        <v>37</v>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>RCV2919565</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D52" s="5" t="n">
-        <v>30286</v>
-      </c>
-      <c r="E52" t="s">
-        <v>38</v>
+        <v>24306</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>46.1</v>
+        <v>39.7</v>
       </c>
       <c r="G52" t="n">
         <v>2</v>
       </c>
-      <c r="H52" t="s">
-        <v>45</v>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I52" s="5" t="n">
         <v>46478</v>
@@ -2704,26 +2614,34 @@
       <c r="A53" t="n">
         <v>52</v>
       </c>
-      <c r="B53" t="s">
-        <v>95</v>
-      </c>
-      <c r="C53" t="s">
-        <v>41</v>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>RCV5510200</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>26312</v>
-      </c>
-      <c r="E53" t="s">
-        <v>42</v>
+        <v>28439</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F53" s="6" t="n">
-        <v>45.8</v>
+        <v>39.4</v>
       </c>
       <c r="G53" t="n">
         <v>2</v>
       </c>
-      <c r="H53" t="s">
-        <v>39</v>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>RN Team B</t>
+        </is>
       </c>
       <c r="I53" s="5" t="n">
         <v>46478</v>
@@ -2733,26 +2651,34 @@
       <c r="A54" t="n">
         <v>53</v>
       </c>
-      <c r="B54" t="s">
-        <v>96</v>
-      </c>
-      <c r="C54" t="s">
-        <v>37</v>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>RCV5168987</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D54" s="5" t="n">
-        <v>26225</v>
-      </c>
-      <c r="E54" t="s">
-        <v>38</v>
+        <v>33637</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>45.8</v>
+        <v>39.3</v>
       </c>
       <c r="G54" t="n">
         <v>2</v>
       </c>
-      <c r="H54" t="s">
-        <v>43</v>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I54" s="5" t="n">
         <v>46478</v>
@@ -2762,26 +2688,34 @@
       <c r="A55" t="n">
         <v>54</v>
       </c>
-      <c r="B55" t="s">
-        <v>97</v>
-      </c>
-      <c r="C55" t="s">
-        <v>37</v>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>RCV5566499</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>32960</v>
-      </c>
-      <c r="E55" t="s">
-        <v>42</v>
+        <v>46134</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F55" s="6" t="n">
-        <v>45.7</v>
+        <v>39.3</v>
       </c>
       <c r="G55" t="n">
         <v>2</v>
       </c>
-      <c r="H55" t="s">
-        <v>45</v>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I55" s="5" t="n">
         <v>46478</v>
@@ -2791,26 +2725,34 @@
       <c r="A56" t="n">
         <v>55</v>
       </c>
-      <c r="B56" t="s">
-        <v>98</v>
-      </c>
-      <c r="C56" t="s">
-        <v>37</v>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>RCV4899050</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D56" s="5" t="n">
-        <v>26541</v>
-      </c>
-      <c r="E56" t="s">
-        <v>38</v>
+        <v>24208</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F56" s="6" t="n">
-        <v>45.4</v>
+        <v>39.1</v>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
-      </c>
-      <c r="H56" t="s">
-        <v>99</v>
+        <v>2</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>RN Team A</t>
+        </is>
       </c>
       <c r="I56" s="5" t="n">
         <v>46478</v>
@@ -2820,26 +2762,34 @@
       <c r="A57" t="n">
         <v>56</v>
       </c>
-      <c r="B57" t="s">
-        <v>100</v>
-      </c>
-      <c r="C57" t="s">
-        <v>37</v>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>RCV1947586</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>26857</v>
-      </c>
-      <c r="E57" t="s">
-        <v>42</v>
+        <v>35326</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F57" s="6" t="n">
-        <v>45.4</v>
+        <v>39.1</v>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
-      </c>
-      <c r="H57" t="s">
-        <v>101</v>
+        <v>2</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I57" s="5" t="n">
         <v>46478</v>
@@ -2849,26 +2799,34 @@
       <c r="A58" t="n">
         <v>57</v>
       </c>
-      <c r="B58" t="s">
-        <v>102</v>
-      </c>
-      <c r="C58" t="s">
-        <v>37</v>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>RCV5863375</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D58" s="5" t="n">
-        <v>23356</v>
-      </c>
-      <c r="E58" t="s">
-        <v>38</v>
+        <v>20965</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F58" s="6" t="n">
-        <v>45.3</v>
+        <v>39</v>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
-      </c>
-      <c r="H58" t="s">
-        <v>99</v>
+        <v>2</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>RN Team A</t>
+        </is>
       </c>
       <c r="I58" s="5" t="n">
         <v>46478</v>
@@ -2878,26 +2836,34 @@
       <c r="A59" t="n">
         <v>58</v>
       </c>
-      <c r="B59" t="s">
-        <v>103</v>
-      </c>
-      <c r="C59" t="s">
-        <v>58</v>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>RCV1203862</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>44818</v>
-      </c>
-      <c r="E59" t="s">
-        <v>38</v>
+        <v>30841</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F59" s="6" t="n">
-        <v>45.1</v>
+        <v>39</v>
       </c>
       <c r="G59" t="n">
-        <v>3</v>
-      </c>
-      <c r="H59" t="s">
-        <v>101</v>
+        <v>2</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I59" s="5" t="n">
         <v>46478</v>
@@ -2907,26 +2873,34 @@
       <c r="A60" t="n">
         <v>59</v>
       </c>
-      <c r="B60" t="s">
-        <v>104</v>
-      </c>
-      <c r="C60" t="s">
-        <v>37</v>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>RCV8834952</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D60" s="5" t="n">
-        <v>23611</v>
-      </c>
-      <c r="E60" t="s">
-        <v>38</v>
+        <v>35129</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F60" s="6" t="n">
-        <v>45.1</v>
+        <v>38.7</v>
       </c>
       <c r="G60" t="n">
-        <v>3</v>
-      </c>
-      <c r="H60" t="s">
-        <v>99</v>
+        <v>2</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I60" s="5" t="n">
         <v>46478</v>
@@ -2936,26 +2910,34 @@
       <c r="A61" t="n">
         <v>60</v>
       </c>
-      <c r="B61" t="s">
-        <v>105</v>
-      </c>
-      <c r="C61" t="s">
-        <v>58</v>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>RCV2810335</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>46271</v>
-      </c>
-      <c r="E61" t="s">
-        <v>42</v>
+        <v>25295</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F61" s="6" t="n">
-        <v>45</v>
+        <v>38.7</v>
       </c>
       <c r="G61" t="n">
-        <v>3</v>
-      </c>
-      <c r="H61" t="s">
-        <v>101</v>
+        <v>2</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>RN Team B</t>
+        </is>
       </c>
       <c r="I61" s="5" t="n">
         <v>46478</v>
@@ -2965,26 +2947,34 @@
       <c r="A62" t="n">
         <v>61</v>
       </c>
-      <c r="B62" t="s">
-        <v>106</v>
-      </c>
-      <c r="C62" t="s">
-        <v>41</v>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>RCV4951271</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D62" s="5" t="n">
-        <v>23333</v>
-      </c>
-      <c r="E62" t="s">
-        <v>38</v>
+        <v>27969</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F62" s="6" t="n">
-        <v>44.8</v>
+        <v>38.7</v>
       </c>
       <c r="G62" t="n">
-        <v>3</v>
-      </c>
-      <c r="H62" t="s">
-        <v>99</v>
+        <v>2</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I62" s="5" t="n">
         <v>46478</v>
@@ -2994,26 +2984,34 @@
       <c r="A63" t="n">
         <v>62</v>
       </c>
-      <c r="B63" t="s">
-        <v>107</v>
-      </c>
-      <c r="C63" t="s">
-        <v>37</v>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>RCV7668760</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>34426</v>
-      </c>
-      <c r="E63" t="s">
-        <v>38</v>
+        <v>37190</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F63" s="6" t="n">
-        <v>44.4</v>
+        <v>38.6</v>
       </c>
       <c r="G63" t="n">
-        <v>3</v>
-      </c>
-      <c r="H63" t="s">
-        <v>101</v>
+        <v>2</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I63" s="5" t="n">
         <v>46478</v>
@@ -3023,26 +3021,34 @@
       <c r="A64" t="n">
         <v>63</v>
       </c>
-      <c r="B64" t="s">
-        <v>108</v>
-      </c>
-      <c r="C64" t="s">
-        <v>41</v>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>RCV9968668</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>33649</v>
-      </c>
-      <c r="E64" t="s">
-        <v>42</v>
+        <v>32548</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F64" s="6" t="n">
-        <v>44.4</v>
+        <v>38.5</v>
       </c>
       <c r="G64" t="n">
-        <v>3</v>
-      </c>
-      <c r="H64" t="s">
-        <v>99</v>
+        <v>2</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I64" s="5" t="n">
         <v>46478</v>
@@ -3052,26 +3058,34 @@
       <c r="A65" t="n">
         <v>64</v>
       </c>
-      <c r="B65" t="s">
-        <v>109</v>
-      </c>
-      <c r="C65" t="s">
-        <v>37</v>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>RCV6032188</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>25360</v>
-      </c>
-      <c r="E65" t="s">
-        <v>42</v>
+        <v>30936</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F65" s="6" t="n">
-        <v>44.4</v>
+        <v>38.5</v>
       </c>
       <c r="G65" t="n">
-        <v>3</v>
-      </c>
-      <c r="H65" t="s">
-        <v>101</v>
+        <v>2</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I65" s="5" t="n">
         <v>46478</v>
@@ -3081,26 +3095,34 @@
       <c r="A66" t="n">
         <v>65</v>
       </c>
-      <c r="B66" t="s">
-        <v>110</v>
-      </c>
-      <c r="C66" t="s">
-        <v>37</v>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>RCV1657905</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D66" s="5" t="n">
-        <v>30791</v>
-      </c>
-      <c r="E66" t="s">
-        <v>42</v>
+        <v>30867</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F66" s="6" t="n">
-        <v>44.3</v>
+        <v>38.4</v>
       </c>
       <c r="G66" t="n">
-        <v>3</v>
-      </c>
-      <c r="H66" t="s">
-        <v>99</v>
+        <v>2</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I66" s="5" t="n">
         <v>46478</v>
@@ -3110,26 +3132,34 @@
       <c r="A67" t="n">
         <v>66</v>
       </c>
-      <c r="B67" t="s">
-        <v>111</v>
-      </c>
-      <c r="C67" t="s">
-        <v>41</v>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>RCV3942326</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>28485</v>
-      </c>
-      <c r="E67" t="s">
-        <v>42</v>
+        <v>27790</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F67" s="6" t="n">
-        <v>44.2</v>
+        <v>38.4</v>
       </c>
       <c r="G67" t="n">
-        <v>3</v>
-      </c>
-      <c r="H67" t="s">
-        <v>101</v>
+        <v>2</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>RN Team B</t>
+        </is>
       </c>
       <c r="I67" s="5" t="n">
         <v>46478</v>
@@ -3139,26 +3169,34 @@
       <c r="A68" t="n">
         <v>67</v>
       </c>
-      <c r="B68" t="s">
-        <v>112</v>
-      </c>
-      <c r="C68" t="s">
-        <v>41</v>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>RCV4533275</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D68" s="5" t="n">
-        <v>30131</v>
-      </c>
-      <c r="E68" t="s">
-        <v>38</v>
+        <v>46224</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F68" s="6" t="n">
-        <v>44.1</v>
+        <v>38.1</v>
       </c>
       <c r="G68" t="n">
-        <v>3</v>
-      </c>
-      <c r="H68" t="s">
-        <v>99</v>
+        <v>2</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I68" s="5" t="n">
         <v>46478</v>
@@ -3168,26 +3206,34 @@
       <c r="A69" t="n">
         <v>68</v>
       </c>
-      <c r="B69" t="s">
-        <v>113</v>
-      </c>
-      <c r="C69" t="s">
-        <v>37</v>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>RCV1315676</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>31451</v>
-      </c>
-      <c r="E69" t="s">
+        <v>27786</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="F69" s="6" t="n">
-        <v>44.1</v>
-      </c>
       <c r="G69" t="n">
-        <v>3</v>
-      </c>
-      <c r="H69" t="s">
-        <v>101</v>
+        <v>2</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I69" s="5" t="n">
         <v>46478</v>
@@ -3197,26 +3243,34 @@
       <c r="A70" t="n">
         <v>69</v>
       </c>
-      <c r="B70" t="s">
-        <v>114</v>
-      </c>
-      <c r="C70" t="s">
-        <v>37</v>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>RCV5283668</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D70" s="5" t="n">
-        <v>23337</v>
-      </c>
-      <c r="E70" t="s">
-        <v>42</v>
+        <v>28947</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F70" s="6" t="n">
-        <v>43.7</v>
+        <v>38</v>
       </c>
       <c r="G70" t="n">
-        <v>3</v>
-      </c>
-      <c r="H70" t="s">
-        <v>99</v>
+        <v>2</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I70" s="5" t="n">
         <v>46478</v>
@@ -3226,26 +3280,34 @@
       <c r="A71" t="n">
         <v>70</v>
       </c>
-      <c r="B71" t="s">
-        <v>115</v>
-      </c>
-      <c r="C71" t="s">
-        <v>41</v>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>RCV5315428</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>28330</v>
-      </c>
-      <c r="E71" t="s">
-        <v>38</v>
+        <v>30154</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F71" s="6" t="n">
-        <v>43.5</v>
+        <v>37.9</v>
       </c>
       <c r="G71" t="n">
-        <v>3</v>
-      </c>
-      <c r="H71" t="s">
-        <v>101</v>
+        <v>2</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I71" s="5" t="n">
         <v>46478</v>
@@ -3255,26 +3317,34 @@
       <c r="A72" t="n">
         <v>71</v>
       </c>
-      <c r="B72" t="s">
-        <v>116</v>
-      </c>
-      <c r="C72" t="s">
-        <v>41</v>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>RCV9495454</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>25130</v>
-      </c>
-      <c r="E72" t="s">
-        <v>42</v>
+        <v>28824</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F72" s="6" t="n">
-        <v>43.5</v>
+        <v>37.9</v>
       </c>
       <c r="G72" t="n">
-        <v>3</v>
-      </c>
-      <c r="H72" t="s">
-        <v>99</v>
+        <v>2</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I72" s="5" t="n">
         <v>46478</v>
@@ -3284,26 +3354,34 @@
       <c r="A73" t="n">
         <v>72</v>
       </c>
-      <c r="B73" t="s">
-        <v>117</v>
-      </c>
-      <c r="C73" t="s">
-        <v>37</v>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>RCV2960214</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>28246</v>
-      </c>
-      <c r="E73" t="s">
-        <v>42</v>
+        <v>27298</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F73" s="6" t="n">
-        <v>43.4</v>
+        <v>37.9</v>
       </c>
       <c r="G73" t="n">
-        <v>3</v>
-      </c>
-      <c r="H73" t="s">
-        <v>101</v>
+        <v>2</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>RN Team C</t>
+        </is>
       </c>
       <c r="I73" s="5" t="n">
         <v>46478</v>
@@ -3313,26 +3391,34 @@
       <c r="A74" t="n">
         <v>73</v>
       </c>
-      <c r="B74" t="s">
-        <v>118</v>
-      </c>
-      <c r="C74" t="s">
-        <v>37</v>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>RCV2409617</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D74" s="5" t="n">
-        <v>29192</v>
-      </c>
-      <c r="E74" t="s">
-        <v>38</v>
+        <v>28877</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F74" s="6" t="n">
-        <v>43.3</v>
+        <v>37.7</v>
       </c>
       <c r="G74" t="n">
         <v>3</v>
       </c>
-      <c r="H74" t="s">
-        <v>99</v>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I74" s="5" t="n">
         <v>46478</v>
@@ -3342,26 +3428,34 @@
       <c r="A75" t="n">
         <v>74</v>
       </c>
-      <c r="B75" t="s">
-        <v>119</v>
-      </c>
-      <c r="C75" t="s">
-        <v>37</v>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>RCV3340479</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>31905</v>
-      </c>
-      <c r="E75" t="s">
-        <v>38</v>
+        <v>33533</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F75" s="6" t="n">
-        <v>43.2</v>
+        <v>37.5</v>
       </c>
       <c r="G75" t="n">
         <v>3</v>
       </c>
-      <c r="H75" t="s">
-        <v>101</v>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I75" s="5" t="n">
         <v>46478</v>
@@ -3371,26 +3465,34 @@
       <c r="A76" t="n">
         <v>75</v>
       </c>
-      <c r="B76" t="s">
-        <v>120</v>
-      </c>
-      <c r="C76" t="s">
-        <v>37</v>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>RCV4210913</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D76" s="5" t="n">
-        <v>26708</v>
-      </c>
-      <c r="E76" t="s">
-        <v>42</v>
+        <v>37516</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>43.1</v>
+        <v>37.5</v>
       </c>
       <c r="G76" t="n">
         <v>3</v>
       </c>
-      <c r="H76" t="s">
-        <v>99</v>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I76" s="5" t="n">
         <v>46478</v>
@@ -3400,26 +3502,34 @@
       <c r="A77" t="n">
         <v>76</v>
       </c>
-      <c r="B77" t="s">
-        <v>121</v>
-      </c>
-      <c r="C77" t="s">
-        <v>41</v>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>RCV1277465</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D77" s="5" t="n">
-        <v>23050</v>
-      </c>
-      <c r="E77" t="s">
-        <v>42</v>
+        <v>27961</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F77" s="6" t="n">
-        <v>42.9</v>
+        <v>37.4</v>
       </c>
       <c r="G77" t="n">
         <v>3</v>
       </c>
-      <c r="H77" t="s">
-        <v>101</v>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I77" s="5" t="n">
         <v>46478</v>
@@ -3429,26 +3539,34 @@
       <c r="A78" t="n">
         <v>77</v>
       </c>
-      <c r="B78" t="s">
-        <v>122</v>
-      </c>
-      <c r="C78" t="s">
-        <v>37</v>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>RCV5591867</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D78" s="5" t="n">
-        <v>29632</v>
-      </c>
-      <c r="E78" t="s">
-        <v>38</v>
+        <v>27813</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F78" s="6" t="n">
-        <v>42.9</v>
+        <v>37.2</v>
       </c>
       <c r="G78" t="n">
         <v>3</v>
       </c>
-      <c r="H78" t="s">
-        <v>99</v>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I78" s="5" t="n">
         <v>46478</v>
@@ -3458,26 +3576,34 @@
       <c r="A79" t="n">
         <v>78</v>
       </c>
-      <c r="B79" t="s">
-        <v>123</v>
-      </c>
-      <c r="C79" t="s">
-        <v>41</v>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>RCV7862809</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D79" s="5" t="n">
-        <v>24947</v>
-      </c>
-      <c r="E79" t="s">
-        <v>42</v>
+        <v>31271</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F79" s="6" t="n">
-        <v>42.4</v>
+        <v>37.2</v>
       </c>
       <c r="G79" t="n">
         <v>3</v>
       </c>
-      <c r="H79" t="s">
-        <v>101</v>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I79" s="5" t="n">
         <v>46478</v>
@@ -3487,26 +3613,34 @@
       <c r="A80" t="n">
         <v>79</v>
       </c>
-      <c r="B80" t="s">
-        <v>124</v>
-      </c>
-      <c r="C80" t="s">
-        <v>37</v>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>RCV8014223</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D80" s="5" t="n">
-        <v>28765</v>
-      </c>
-      <c r="E80" t="s">
-        <v>38</v>
+        <v>27902</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F80" s="6" t="n">
-        <v>42.1</v>
+        <v>37.1</v>
       </c>
       <c r="G80" t="n">
         <v>3</v>
       </c>
-      <c r="H80" t="s">
-        <v>99</v>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I80" s="5" t="n">
         <v>46478</v>
@@ -3516,26 +3650,34 @@
       <c r="A81" t="n">
         <v>80</v>
       </c>
-      <c r="B81" t="s">
-        <v>125</v>
-      </c>
-      <c r="C81" t="s">
-        <v>37</v>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>RCV7061717</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D81" s="5" t="n">
-        <v>24183</v>
-      </c>
-      <c r="E81" t="s">
-        <v>38</v>
+        <v>43283</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F81" s="6" t="n">
-        <v>42.1</v>
+        <v>37.1</v>
       </c>
       <c r="G81" t="n">
         <v>3</v>
       </c>
-      <c r="H81" t="s">
-        <v>101</v>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I81" s="5" t="n">
         <v>46478</v>
@@ -3545,26 +3687,34 @@
       <c r="A82" t="n">
         <v>81</v>
       </c>
-      <c r="B82" t="s">
-        <v>126</v>
-      </c>
-      <c r="C82" t="s">
-        <v>41</v>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>RCV4467829</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D82" s="5" t="n">
-        <v>26702</v>
-      </c>
-      <c r="E82" t="s">
-        <v>42</v>
+        <v>37122</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F82" s="6" t="n">
-        <v>42.1</v>
+        <v>37.1</v>
       </c>
       <c r="G82" t="n">
         <v>3</v>
       </c>
-      <c r="H82" t="s">
-        <v>99</v>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I82" s="5" t="n">
         <v>46478</v>
@@ -3574,26 +3724,34 @@
       <c r="A83" t="n">
         <v>82</v>
       </c>
-      <c r="B83" t="s">
-        <v>127</v>
-      </c>
-      <c r="C83" t="s">
-        <v>37</v>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>RCV9437872</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D83" s="5" t="n">
-        <v>23903</v>
-      </c>
-      <c r="E83" t="s">
-        <v>38</v>
+        <v>29427</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F83" s="6" t="n">
-        <v>42.1</v>
+        <v>37.1</v>
       </c>
       <c r="G83" t="n">
         <v>3</v>
       </c>
-      <c r="H83" t="s">
-        <v>101</v>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I83" s="5" t="n">
         <v>46478</v>
@@ -3603,26 +3761,34 @@
       <c r="A84" t="n">
         <v>83</v>
       </c>
-      <c r="B84" t="s">
-        <v>128</v>
-      </c>
-      <c r="C84" t="s">
-        <v>41</v>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>RCV5279940</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D84" s="5" t="n">
-        <v>25180</v>
-      </c>
-      <c r="E84" t="s">
-        <v>42</v>
+        <v>23734</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F84" s="6" t="n">
-        <v>42</v>
+        <v>36.9</v>
       </c>
       <c r="G84" t="n">
         <v>3</v>
       </c>
-      <c r="H84" t="s">
-        <v>99</v>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I84" s="5" t="n">
         <v>46478</v>
@@ -3632,26 +3798,34 @@
       <c r="A85" t="n">
         <v>84</v>
       </c>
-      <c r="B85" t="s">
-        <v>129</v>
-      </c>
-      <c r="C85" t="s">
-        <v>37</v>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>RCV1937360</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D85" s="5" t="n">
-        <v>23171</v>
-      </c>
-      <c r="E85" t="s">
-        <v>42</v>
+        <v>33054</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F85" s="6" t="n">
-        <v>41.9</v>
+        <v>36.9</v>
       </c>
       <c r="G85" t="n">
         <v>3</v>
       </c>
-      <c r="H85" t="s">
-        <v>101</v>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I85" s="5" t="n">
         <v>46478</v>
@@ -3661,26 +3835,34 @@
       <c r="A86" t="n">
         <v>85</v>
       </c>
-      <c r="B86" t="s">
-        <v>130</v>
-      </c>
-      <c r="C86" t="s">
-        <v>37</v>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>RCV9952179</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D86" s="5" t="n">
-        <v>31499</v>
-      </c>
-      <c r="E86" t="s">
-        <v>38</v>
+        <v>26412</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F86" s="6" t="n">
-        <v>41.8</v>
+        <v>36.9</v>
       </c>
       <c r="G86" t="n">
         <v>3</v>
       </c>
-      <c r="H86" t="s">
-        <v>99</v>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I86" s="5" t="n">
         <v>46478</v>
@@ -3690,26 +3872,34 @@
       <c r="A87" t="n">
         <v>86</v>
       </c>
-      <c r="B87" t="s">
-        <v>131</v>
-      </c>
-      <c r="C87" t="s">
-        <v>41</v>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>RCV2975871</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D87" s="5" t="n">
-        <v>24113</v>
-      </c>
-      <c r="E87" t="s">
-        <v>42</v>
+        <v>29352</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F87" s="6" t="n">
-        <v>41.7</v>
+        <v>36.8</v>
       </c>
       <c r="G87" t="n">
         <v>3</v>
       </c>
-      <c r="H87" t="s">
-        <v>101</v>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I87" s="5" t="n">
         <v>46478</v>
@@ -3719,26 +3909,34 @@
       <c r="A88" t="n">
         <v>87</v>
       </c>
-      <c r="B88" t="s">
-        <v>132</v>
-      </c>
-      <c r="C88" t="s">
-        <v>37</v>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>RCV8621093</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D88" s="5" t="n">
-        <v>31691</v>
-      </c>
-      <c r="E88" t="s">
-        <v>42</v>
+        <v>31277</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F88" s="6" t="n">
-        <v>41.7</v>
+        <v>36.7</v>
       </c>
       <c r="G88" t="n">
         <v>3</v>
       </c>
-      <c r="H88" t="s">
-        <v>99</v>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I88" s="5" t="n">
         <v>46478</v>
@@ -3748,26 +3946,34 @@
       <c r="A89" t="n">
         <v>88</v>
       </c>
-      <c r="B89" t="s">
-        <v>133</v>
-      </c>
-      <c r="C89" t="s">
-        <v>41</v>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>RCV6197369</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D89" s="5" t="n">
-        <v>33615</v>
-      </c>
-      <c r="E89" t="s">
-        <v>38</v>
+        <v>35840</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F89" s="6" t="n">
-        <v>41.5</v>
+        <v>36.6</v>
       </c>
       <c r="G89" t="n">
         <v>3</v>
       </c>
-      <c r="H89" t="s">
-        <v>101</v>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I89" s="5" t="n">
         <v>46478</v>
@@ -3777,26 +3983,34 @@
       <c r="A90" t="n">
         <v>89</v>
       </c>
-      <c r="B90" t="s">
-        <v>134</v>
-      </c>
-      <c r="C90" t="s">
-        <v>37</v>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>RCV1523489</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D90" s="5" t="n">
-        <v>23801</v>
-      </c>
-      <c r="E90" t="s">
-        <v>38</v>
+        <v>24655</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F90" s="6" t="n">
-        <v>41.4</v>
+        <v>36.6</v>
       </c>
       <c r="G90" t="n">
         <v>3</v>
       </c>
-      <c r="H90" t="s">
-        <v>99</v>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I90" s="5" t="n">
         <v>46478</v>
@@ -3806,26 +4020,34 @@
       <c r="A91" t="n">
         <v>90</v>
       </c>
-      <c r="B91" t="s">
-        <v>135</v>
-      </c>
-      <c r="C91" t="s">
-        <v>37</v>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>RCV5710113</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D91" s="5" t="n">
-        <v>33777</v>
-      </c>
-      <c r="E91" t="s">
-        <v>38</v>
+        <v>26352</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F91" s="6" t="n">
-        <v>41.3</v>
+        <v>36.4</v>
       </c>
       <c r="G91" t="n">
         <v>3</v>
       </c>
-      <c r="H91" t="s">
-        <v>101</v>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I91" s="5" t="n">
         <v>46478</v>
@@ -3835,26 +4057,34 @@
       <c r="A92" t="n">
         <v>91</v>
       </c>
-      <c r="B92" t="s">
-        <v>136</v>
-      </c>
-      <c r="C92" t="s">
-        <v>37</v>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>RCV7304462</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D92" s="5" t="n">
-        <v>23163</v>
-      </c>
-      <c r="E92" t="s">
-        <v>42</v>
+        <v>25208</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F92" s="6" t="n">
-        <v>41.1</v>
+        <v>36.3</v>
       </c>
       <c r="G92" t="n">
         <v>3</v>
       </c>
-      <c r="H92" t="s">
-        <v>99</v>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I92" s="5" t="n">
         <v>46478</v>
@@ -3864,26 +4094,34 @@
       <c r="A93" t="n">
         <v>92</v>
       </c>
-      <c r="B93" t="s">
-        <v>137</v>
-      </c>
-      <c r="C93" t="s">
-        <v>58</v>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>RCV3448604</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D93" s="5" t="n">
-        <v>40371</v>
-      </c>
-      <c r="E93" t="s">
-        <v>42</v>
+        <v>32216</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F93" s="6" t="n">
-        <v>40.9</v>
+        <v>36.3</v>
       </c>
       <c r="G93" t="n">
         <v>3</v>
       </c>
-      <c r="H93" t="s">
-        <v>101</v>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I93" s="5" t="n">
         <v>46478</v>
@@ -3893,26 +4131,34 @@
       <c r="A94" t="n">
         <v>93</v>
       </c>
-      <c r="B94" t="s">
-        <v>138</v>
-      </c>
-      <c r="C94" t="s">
-        <v>37</v>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>RCV5746488</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D94" s="5" t="n">
-        <v>30584</v>
-      </c>
-      <c r="E94" t="s">
-        <v>42</v>
+        <v>46315</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F94" s="6" t="n">
-        <v>40.9</v>
+        <v>36.3</v>
       </c>
       <c r="G94" t="n">
         <v>3</v>
       </c>
-      <c r="H94" t="s">
-        <v>99</v>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I94" s="5" t="n">
         <v>46478</v>
@@ -3922,26 +4168,34 @@
       <c r="A95" t="n">
         <v>94</v>
       </c>
-      <c r="B95" t="s">
-        <v>139</v>
-      </c>
-      <c r="C95" t="s">
-        <v>37</v>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>RCV2632014</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D95" s="5" t="n">
-        <v>23210</v>
-      </c>
-      <c r="E95" t="s">
-        <v>42</v>
+        <v>23907</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F95" s="6" t="n">
-        <v>40.8</v>
+        <v>36.3</v>
       </c>
       <c r="G95" t="n">
         <v>3</v>
       </c>
-      <c r="H95" t="s">
-        <v>101</v>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I95" s="5" t="n">
         <v>46478</v>
@@ -3951,26 +4205,34 @@
       <c r="A96" t="n">
         <v>95</v>
       </c>
-      <c r="B96" t="s">
-        <v>140</v>
-      </c>
-      <c r="C96" t="s">
-        <v>37</v>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>RCV6769341</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D96" s="5" t="n">
-        <v>24564</v>
-      </c>
-      <c r="E96" t="s">
-        <v>38</v>
+        <v>24072</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F96" s="6" t="n">
-        <v>40.7</v>
+        <v>36.3</v>
       </c>
       <c r="G96" t="n">
         <v>3</v>
       </c>
-      <c r="H96" t="s">
-        <v>99</v>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I96" s="5" t="n">
         <v>46478</v>
@@ -3980,26 +4242,34 @@
       <c r="A97" t="n">
         <v>96</v>
       </c>
-      <c r="B97" t="s">
-        <v>141</v>
-      </c>
-      <c r="C97" t="s">
-        <v>41</v>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>RCV3217981</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D97" s="5" t="n">
-        <v>29070</v>
-      </c>
-      <c r="E97" t="s">
-        <v>42</v>
+        <v>28198</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F97" s="6" t="n">
-        <v>40.6</v>
+        <v>36.2</v>
       </c>
       <c r="G97" t="n">
         <v>3</v>
       </c>
-      <c r="H97" t="s">
-        <v>101</v>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I97" s="5" t="n">
         <v>46478</v>
@@ -4009,26 +4279,34 @@
       <c r="A98" t="n">
         <v>97</v>
       </c>
-      <c r="B98" t="s">
-        <v>142</v>
-      </c>
-      <c r="C98" t="s">
-        <v>41</v>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>RCV2747077</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D98" s="5" t="n">
-        <v>29158</v>
-      </c>
-      <c r="E98" t="s">
-        <v>38</v>
+        <v>28998</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F98" s="6" t="n">
-        <v>40.5</v>
+        <v>36.2</v>
       </c>
       <c r="G98" t="n">
         <v>3</v>
       </c>
-      <c r="H98" t="s">
-        <v>99</v>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I98" s="5" t="n">
         <v>46478</v>
@@ -4038,26 +4316,34 @@
       <c r="A99" t="n">
         <v>98</v>
       </c>
-      <c r="B99" t="s">
-        <v>143</v>
-      </c>
-      <c r="C99" t="s">
-        <v>58</v>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>RCV9766459</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D99" s="5" t="n">
-        <v>46084</v>
-      </c>
-      <c r="E99" t="s">
-        <v>38</v>
+        <v>24804</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F99" s="6" t="n">
-        <v>40.3</v>
+        <v>36.1</v>
       </c>
       <c r="G99" t="n">
         <v>3</v>
       </c>
-      <c r="H99" t="s">
-        <v>101</v>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I99" s="5" t="n">
         <v>46478</v>
@@ -4067,26 +4353,34 @@
       <c r="A100" t="n">
         <v>99</v>
       </c>
-      <c r="B100" t="s">
-        <v>144</v>
-      </c>
-      <c r="C100" t="s">
-        <v>58</v>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>RCV6190692</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D100" s="5" t="n">
-        <v>44577</v>
-      </c>
-      <c r="E100" t="s">
-        <v>42</v>
+        <v>30533</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F100" s="6" t="n">
-        <v>40.3</v>
+        <v>36.1</v>
       </c>
       <c r="G100" t="n">
         <v>3</v>
       </c>
-      <c r="H100" t="s">
-        <v>99</v>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I100" s="5" t="n">
         <v>46478</v>
@@ -4096,26 +4390,34 @@
       <c r="A101" t="n">
         <v>100</v>
       </c>
-      <c r="B101" t="s">
-        <v>145</v>
-      </c>
-      <c r="C101" t="s">
-        <v>58</v>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>RCV4869334</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>44701</v>
-      </c>
-      <c r="E101" t="s">
-        <v>42</v>
+        <v>26404</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F101" s="6" t="n">
-        <v>40.2</v>
+        <v>35.9</v>
       </c>
       <c r="G101" t="n">
         <v>3</v>
       </c>
-      <c r="H101" t="s">
-        <v>101</v>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I101" s="5" t="n">
         <v>46478</v>
@@ -4125,26 +4427,34 @@
       <c r="A102" t="n">
         <v>101</v>
       </c>
-      <c r="B102" t="s">
-        <v>146</v>
-      </c>
-      <c r="C102" t="s">
-        <v>41</v>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>RCV7845029</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D102" s="5" t="n">
-        <v>28315</v>
-      </c>
-      <c r="E102" t="s">
-        <v>38</v>
+        <v>26342</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F102" s="6" t="n">
-        <v>40.1</v>
+        <v>35.9</v>
       </c>
       <c r="G102" t="n">
         <v>3</v>
       </c>
-      <c r="H102" t="s">
-        <v>99</v>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I102" s="5" t="n">
         <v>46478</v>
@@ -4154,26 +4464,34 @@
       <c r="A103" t="n">
         <v>102</v>
       </c>
-      <c r="B103" t="s">
-        <v>147</v>
-      </c>
-      <c r="C103" t="s">
-        <v>37</v>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>RCV1071872</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D103" s="5" t="n">
-        <v>36884</v>
-      </c>
-      <c r="E103" t="s">
-        <v>42</v>
+        <v>26578</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F103" s="6" t="n">
-        <v>40</v>
+        <v>35.9</v>
       </c>
       <c r="G103" t="n">
         <v>3</v>
       </c>
-      <c r="H103" t="s">
-        <v>101</v>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I103" s="5" t="n">
         <v>46478</v>
@@ -4183,26 +4501,34 @@
       <c r="A104" t="n">
         <v>103</v>
       </c>
-      <c r="B104" t="s">
-        <v>148</v>
-      </c>
-      <c r="C104" t="s">
-        <v>37</v>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>RCV1913391</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D104" s="5" t="n">
-        <v>33343</v>
-      </c>
-      <c r="E104" t="s">
-        <v>38</v>
+        <v>27834</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F104" s="6" t="n">
-        <v>39.9</v>
+        <v>35.9</v>
       </c>
       <c r="G104" t="n">
-        <v>4</v>
-      </c>
-      <c r="H104" t="s">
-        <v>99</v>
+        <v>3</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I104" s="5" t="n">
         <v>46478</v>
@@ -4212,26 +4538,34 @@
       <c r="A105" t="n">
         <v>104</v>
       </c>
-      <c r="B105" t="s">
-        <v>149</v>
-      </c>
-      <c r="C105" t="s">
-        <v>37</v>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>RCV9121410</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D105" s="5" t="n">
-        <v>23803</v>
-      </c>
-      <c r="E105" t="s">
-        <v>42</v>
+        <v>28952</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F105" s="6" t="n">
-        <v>39.7</v>
+        <v>35.9</v>
       </c>
       <c r="G105" t="n">
-        <v>4</v>
-      </c>
-      <c r="H105" t="s">
-        <v>101</v>
+        <v>3</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I105" s="5" t="n">
         <v>46478</v>
@@ -4241,26 +4575,34 @@
       <c r="A106" t="n">
         <v>105</v>
       </c>
-      <c r="B106" t="s">
-        <v>150</v>
-      </c>
-      <c r="C106" t="s">
-        <v>37</v>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>RCV6528527</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D106" s="5" t="n">
-        <v>24814</v>
-      </c>
-      <c r="E106" t="s">
-        <v>38</v>
+        <v>23942</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F106" s="6" t="n">
-        <v>39.7</v>
+        <v>35.8</v>
       </c>
       <c r="G106" t="n">
-        <v>4</v>
-      </c>
-      <c r="H106" t="s">
-        <v>99</v>
+        <v>3</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I106" s="5" t="n">
         <v>46478</v>
@@ -4270,26 +4612,34 @@
       <c r="A107" t="n">
         <v>106</v>
       </c>
-      <c r="B107" t="s">
-        <v>151</v>
-      </c>
-      <c r="C107" t="s">
-        <v>37</v>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>RCV5515162</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D107" s="5" t="n">
-        <v>23249</v>
-      </c>
-      <c r="E107" t="s">
-        <v>38</v>
+        <v>24710</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F107" s="6" t="n">
-        <v>39.7</v>
+        <v>35.8</v>
       </c>
       <c r="G107" t="n">
-        <v>4</v>
-      </c>
-      <c r="H107" t="s">
-        <v>101</v>
+        <v>3</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I107" s="5" t="n">
         <v>46478</v>
@@ -4299,26 +4649,34 @@
       <c r="A108" t="n">
         <v>107</v>
       </c>
-      <c r="B108" t="s">
-        <v>152</v>
-      </c>
-      <c r="C108" t="s">
-        <v>58</v>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>RCV9868322</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D108" s="5" t="n">
-        <v>44507</v>
-      </c>
-      <c r="E108" t="s">
-        <v>42</v>
+        <v>29832</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F108" s="6" t="n">
-        <v>39.7</v>
+        <v>35.8</v>
       </c>
       <c r="G108" t="n">
-        <v>4</v>
-      </c>
-      <c r="H108" t="s">
-        <v>99</v>
+        <v>3</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I108" s="5" t="n">
         <v>46478</v>
@@ -4328,26 +4686,34 @@
       <c r="A109" t="n">
         <v>108</v>
       </c>
-      <c r="B109" t="s">
-        <v>153</v>
-      </c>
-      <c r="C109" t="s">
-        <v>37</v>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>RCV2747974</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D109" s="5" t="n">
-        <v>32180</v>
-      </c>
-      <c r="E109" t="s">
-        <v>38</v>
+        <v>23888</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F109" s="6" t="n">
-        <v>39.6</v>
+        <v>35.7</v>
       </c>
       <c r="G109" t="n">
-        <v>4</v>
-      </c>
-      <c r="H109" t="s">
-        <v>101</v>
+        <v>3</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I109" s="5" t="n">
         <v>46478</v>
@@ -4357,26 +4723,34 @@
       <c r="A110" t="n">
         <v>109</v>
       </c>
-      <c r="B110" t="s">
-        <v>154</v>
-      </c>
-      <c r="C110" t="s">
-        <v>41</v>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>RCV8318861</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D110" s="5" t="n">
-        <v>31225</v>
-      </c>
-      <c r="E110" t="s">
-        <v>38</v>
+        <v>24802</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F110" s="6" t="n">
-        <v>39.4</v>
+        <v>35.7</v>
       </c>
       <c r="G110" t="n">
-        <v>4</v>
-      </c>
-      <c r="H110" t="s">
-        <v>99</v>
+        <v>3</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I110" s="5" t="n">
         <v>46478</v>
@@ -4386,26 +4760,34 @@
       <c r="A111" t="n">
         <v>110</v>
       </c>
-      <c r="B111" t="s">
-        <v>155</v>
-      </c>
-      <c r="C111" t="s">
-        <v>37</v>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>RCV6796246</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D111" s="5" t="n">
-        <v>27193</v>
-      </c>
-      <c r="E111" t="s">
-        <v>42</v>
+        <v>37581</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F111" s="6" t="n">
-        <v>39.3</v>
+        <v>35.7</v>
       </c>
       <c r="G111" t="n">
-        <v>4</v>
-      </c>
-      <c r="H111" t="s">
-        <v>101</v>
+        <v>3</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I111" s="5" t="n">
         <v>46478</v>
@@ -4415,26 +4797,34 @@
       <c r="A112" t="n">
         <v>111</v>
       </c>
-      <c r="B112" t="s">
-        <v>156</v>
-      </c>
-      <c r="C112" t="s">
-        <v>37</v>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>RCV5346787</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D112" s="5" t="n">
-        <v>33357</v>
-      </c>
-      <c r="E112" t="s">
-        <v>38</v>
+        <v>24109</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F112" s="6" t="n">
-        <v>39.2</v>
+        <v>35.6</v>
       </c>
       <c r="G112" t="n">
         <v>4</v>
       </c>
-      <c r="H112" t="s">
-        <v>99</v>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I112" s="5" t="n">
         <v>46478</v>
@@ -4444,26 +4834,34 @@
       <c r="A113" t="n">
         <v>112</v>
       </c>
-      <c r="B113" t="s">
-        <v>157</v>
-      </c>
-      <c r="C113" t="s">
-        <v>58</v>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>RCV2283246</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D113" s="5" t="n">
-        <v>42862</v>
-      </c>
-      <c r="E113" t="s">
-        <v>42</v>
+        <v>25235</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F113" s="6" t="n">
-        <v>39.1</v>
+        <v>35.4</v>
       </c>
       <c r="G113" t="n">
         <v>4</v>
       </c>
-      <c r="H113" t="s">
-        <v>101</v>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I113" s="5" t="n">
         <v>46478</v>
@@ -4473,26 +4871,34 @@
       <c r="A114" t="n">
         <v>113</v>
       </c>
-      <c r="B114" t="s">
-        <v>158</v>
-      </c>
-      <c r="C114" t="s">
-        <v>37</v>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>RCV5202951</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D114" s="5" t="n">
-        <v>27649</v>
-      </c>
-      <c r="E114" t="s">
-        <v>38</v>
+        <v>26983</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F114" s="6" t="n">
-        <v>39.1</v>
+        <v>35.4</v>
       </c>
       <c r="G114" t="n">
         <v>4</v>
       </c>
-      <c r="H114" t="s">
-        <v>99</v>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I114" s="5" t="n">
         <v>46478</v>
@@ -4502,26 +4908,34 @@
       <c r="A115" t="n">
         <v>114</v>
       </c>
-      <c r="B115" t="s">
-        <v>159</v>
-      </c>
-      <c r="C115" t="s">
-        <v>37</v>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>RCV5380081</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D115" s="5" t="n">
-        <v>32346</v>
-      </c>
-      <c r="E115" t="s">
-        <v>42</v>
+        <v>30367</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F115" s="6" t="n">
-        <v>39.1</v>
+        <v>35.3</v>
       </c>
       <c r="G115" t="n">
         <v>4</v>
       </c>
-      <c r="H115" t="s">
-        <v>101</v>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I115" s="5" t="n">
         <v>46478</v>
@@ -4531,26 +4945,34 @@
       <c r="A116" t="n">
         <v>115</v>
       </c>
-      <c r="B116" t="s">
-        <v>160</v>
-      </c>
-      <c r="C116" t="s">
-        <v>41</v>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>RCV9761816</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D116" s="5" t="n">
-        <v>22577</v>
-      </c>
-      <c r="E116" t="s">
-        <v>42</v>
+        <v>33923</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F116" s="6" t="n">
-        <v>39</v>
+        <v>35.3</v>
       </c>
       <c r="G116" t="n">
         <v>4</v>
       </c>
-      <c r="H116" t="s">
-        <v>99</v>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I116" s="5" t="n">
         <v>46478</v>
@@ -4560,26 +4982,34 @@
       <c r="A117" t="n">
         <v>116</v>
       </c>
-      <c r="B117" t="s">
-        <v>161</v>
-      </c>
-      <c r="C117" t="s">
-        <v>58</v>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>RCV4711403</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D117" s="5" t="n">
-        <v>43880</v>
-      </c>
-      <c r="E117" t="s">
-        <v>42</v>
+        <v>30268</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F117" s="6" t="n">
-        <v>39</v>
+        <v>35.2</v>
       </c>
       <c r="G117" t="n">
         <v>4</v>
       </c>
-      <c r="H117" t="s">
-        <v>101</v>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I117" s="5" t="n">
         <v>46478</v>
@@ -4589,26 +5019,34 @@
       <c r="A118" t="n">
         <v>117</v>
       </c>
-      <c r="B118" t="s">
-        <v>162</v>
-      </c>
-      <c r="C118" t="s">
-        <v>41</v>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>RCV3189078</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D118" s="5" t="n">
-        <v>28732</v>
-      </c>
-      <c r="E118" t="s">
-        <v>42</v>
+        <v>26567</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F118" s="6" t="n">
-        <v>38.9</v>
+        <v>35.2</v>
       </c>
       <c r="G118" t="n">
         <v>4</v>
       </c>
-      <c r="H118" t="s">
-        <v>99</v>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I118" s="5" t="n">
         <v>46478</v>
@@ -4618,26 +5056,34 @@
       <c r="A119" t="n">
         <v>118</v>
       </c>
-      <c r="B119" t="s">
-        <v>163</v>
-      </c>
-      <c r="C119" t="s">
-        <v>37</v>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>RCV4756035</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D119" s="5" t="n">
-        <v>25840</v>
-      </c>
-      <c r="E119" t="s">
-        <v>38</v>
+        <v>32179</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F119" s="6" t="n">
-        <v>38.8</v>
+        <v>35.2</v>
       </c>
       <c r="G119" t="n">
         <v>4</v>
       </c>
-      <c r="H119" t="s">
-        <v>101</v>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I119" s="5" t="n">
         <v>46478</v>
@@ -4647,26 +5093,34 @@
       <c r="A120" t="n">
         <v>119</v>
       </c>
-      <c r="B120" t="s">
-        <v>164</v>
-      </c>
-      <c r="C120" t="s">
-        <v>58</v>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>RCV1123220</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D120" s="5" t="n">
-        <v>40654</v>
-      </c>
-      <c r="E120" t="s">
-        <v>38</v>
+        <v>40929</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F120" s="6" t="n">
-        <v>38.6</v>
+        <v>35.2</v>
       </c>
       <c r="G120" t="n">
         <v>4</v>
       </c>
-      <c r="H120" t="s">
-        <v>99</v>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I120" s="5" t="n">
         <v>46478</v>
@@ -4676,26 +5130,34 @@
       <c r="A121" t="n">
         <v>120</v>
       </c>
-      <c r="B121" t="s">
-        <v>165</v>
-      </c>
-      <c r="C121" t="s">
-        <v>37</v>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>RCV5866544</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D121" s="5" t="n">
-        <v>26858</v>
-      </c>
-      <c r="E121" t="s">
-        <v>42</v>
+        <v>26442</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F121" s="6" t="n">
-        <v>38.5</v>
+        <v>35</v>
       </c>
       <c r="G121" t="n">
         <v>4</v>
       </c>
-      <c r="H121" t="s">
-        <v>101</v>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I121" s="5" t="n">
         <v>46478</v>
@@ -4705,26 +5167,34 @@
       <c r="A122" t="n">
         <v>121</v>
       </c>
-      <c r="B122" t="s">
-        <v>166</v>
-      </c>
-      <c r="C122" t="s">
-        <v>37</v>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>RCV4268380</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D122" s="5" t="n">
-        <v>23075</v>
-      </c>
-      <c r="E122" t="s">
-        <v>38</v>
+        <v>46273</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F122" s="6" t="n">
-        <v>38.5</v>
+        <v>35</v>
       </c>
       <c r="G122" t="n">
         <v>4</v>
       </c>
-      <c r="H122" t="s">
-        <v>99</v>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I122" s="5" t="n">
         <v>46478</v>
@@ -4734,26 +5204,34 @@
       <c r="A123" t="n">
         <v>122</v>
       </c>
-      <c r="B123" t="s">
-        <v>167</v>
-      </c>
-      <c r="C123" t="s">
-        <v>37</v>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>RCV9596296</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D123" s="5" t="n">
-        <v>30219</v>
-      </c>
-      <c r="E123" t="s">
-        <v>38</v>
+        <v>35110</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F123" s="6" t="n">
-        <v>38.5</v>
+        <v>34.9</v>
       </c>
       <c r="G123" t="n">
         <v>4</v>
       </c>
-      <c r="H123" t="s">
-        <v>101</v>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I123" s="5" t="n">
         <v>46478</v>
@@ -4763,26 +5241,34 @@
       <c r="A124" t="n">
         <v>123</v>
       </c>
-      <c r="B124" t="s">
-        <v>168</v>
-      </c>
-      <c r="C124" t="s">
-        <v>37</v>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>RCV7028261</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D124" s="5" t="n">
-        <v>32281</v>
-      </c>
-      <c r="E124" t="s">
-        <v>38</v>
+        <v>33353</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F124" s="6" t="n">
-        <v>38.5</v>
+        <v>34.8</v>
       </c>
       <c r="G124" t="n">
         <v>4</v>
       </c>
-      <c r="H124" t="s">
-        <v>99</v>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I124" s="5" t="n">
         <v>46478</v>
@@ -4792,26 +5278,34 @@
       <c r="A125" t="n">
         <v>124</v>
       </c>
-      <c r="B125" t="s">
-        <v>169</v>
-      </c>
-      <c r="C125" t="s">
-        <v>58</v>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>RCV3651381</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D125" s="5" t="n">
-        <v>42192</v>
-      </c>
-      <c r="E125" t="s">
-        <v>38</v>
+        <v>22917</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F125" s="6" t="n">
-        <v>38.4</v>
+        <v>34.8</v>
       </c>
       <c r="G125" t="n">
         <v>4</v>
       </c>
-      <c r="H125" t="s">
-        <v>101</v>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I125" s="5" t="n">
         <v>46478</v>
@@ -4821,26 +5315,34 @@
       <c r="A126" t="n">
         <v>125</v>
       </c>
-      <c r="B126" t="s">
-        <v>170</v>
-      </c>
-      <c r="C126" t="s">
-        <v>37</v>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>RCV5755390</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D126" s="5" t="n">
-        <v>37179</v>
-      </c>
-      <c r="E126" t="s">
-        <v>38</v>
+        <v>26511</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F126" s="6" t="n">
-        <v>38.4</v>
+        <v>34.8</v>
       </c>
       <c r="G126" t="n">
         <v>4</v>
       </c>
-      <c r="H126" t="s">
-        <v>99</v>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I126" s="5" t="n">
         <v>46478</v>
@@ -4850,26 +5352,34 @@
       <c r="A127" t="n">
         <v>126</v>
       </c>
-      <c r="B127" t="s">
-        <v>171</v>
-      </c>
-      <c r="C127" t="s">
-        <v>37</v>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>RCV7948468</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D127" s="5" t="n">
-        <v>26701</v>
-      </c>
-      <c r="E127" t="s">
-        <v>42</v>
+        <v>30313</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F127" s="6" t="n">
-        <v>38.4</v>
+        <v>34.7</v>
       </c>
       <c r="G127" t="n">
         <v>4</v>
       </c>
-      <c r="H127" t="s">
-        <v>101</v>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I127" s="5" t="n">
         <v>46478</v>
@@ -4879,26 +5389,34 @@
       <c r="A128" t="n">
         <v>127</v>
       </c>
-      <c r="B128" t="s">
-        <v>172</v>
-      </c>
-      <c r="C128" t="s">
-        <v>37</v>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>RCV2102741</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D128" s="5" t="n">
-        <v>30656</v>
-      </c>
-      <c r="E128" t="s">
-        <v>38</v>
+        <v>24658</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F128" s="6" t="n">
-        <v>38.4</v>
+        <v>34.7</v>
       </c>
       <c r="G128" t="n">
         <v>4</v>
       </c>
-      <c r="H128" t="s">
-        <v>99</v>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I128" s="5" t="n">
         <v>46478</v>
@@ -4908,26 +5426,34 @@
       <c r="A129" t="n">
         <v>128</v>
       </c>
-      <c r="B129" t="s">
-        <v>173</v>
-      </c>
-      <c r="C129" t="s">
-        <v>58</v>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>RCV4477427</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D129" s="5" t="n">
-        <v>46161</v>
-      </c>
-      <c r="E129" t="s">
-        <v>42</v>
+        <v>26813</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F129" s="6" t="n">
-        <v>38.2</v>
+        <v>34.7</v>
       </c>
       <c r="G129" t="n">
         <v>4</v>
       </c>
-      <c r="H129" t="s">
-        <v>101</v>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I129" s="5" t="n">
         <v>46478</v>
@@ -4937,26 +5463,34 @@
       <c r="A130" t="n">
         <v>129</v>
       </c>
-      <c r="B130" t="s">
-        <v>174</v>
-      </c>
-      <c r="C130" t="s">
-        <v>37</v>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>RCV8733567</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D130" s="5" t="n">
-        <v>24876</v>
-      </c>
-      <c r="E130" t="s">
-        <v>38</v>
+        <v>29775</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F130" s="6" t="n">
-        <v>38.2</v>
+        <v>34.6</v>
       </c>
       <c r="G130" t="n">
         <v>4</v>
       </c>
-      <c r="H130" t="s">
-        <v>99</v>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I130" s="5" t="n">
         <v>46478</v>
@@ -4966,26 +5500,34 @@
       <c r="A131" t="n">
         <v>130</v>
       </c>
-      <c r="B131" t="s">
-        <v>175</v>
-      </c>
-      <c r="C131" t="s">
-        <v>37</v>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>RCV1589842</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D131" s="5" t="n">
-        <v>27341</v>
-      </c>
-      <c r="E131" t="s">
-        <v>42</v>
+        <v>25677</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F131" s="6" t="n">
-        <v>38.2</v>
+        <v>34.6</v>
       </c>
       <c r="G131" t="n">
         <v>4</v>
       </c>
-      <c r="H131" t="s">
-        <v>101</v>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I131" s="5" t="n">
         <v>46478</v>
@@ -4995,26 +5537,34 @@
       <c r="A132" t="n">
         <v>131</v>
       </c>
-      <c r="B132" t="s">
-        <v>176</v>
-      </c>
-      <c r="C132" t="s">
-        <v>41</v>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>RCV8057849</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D132" s="5" t="n">
-        <v>22804</v>
-      </c>
-      <c r="E132" t="s">
-        <v>38</v>
+        <v>25491</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F132" s="6" t="n">
-        <v>38.1</v>
+        <v>34.6</v>
       </c>
       <c r="G132" t="n">
         <v>4</v>
       </c>
-      <c r="H132" t="s">
-        <v>99</v>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I132" s="5" t="n">
         <v>46478</v>
@@ -5024,26 +5574,34 @@
       <c r="A133" t="n">
         <v>132</v>
       </c>
-      <c r="B133" t="s">
-        <v>177</v>
-      </c>
-      <c r="C133" t="s">
-        <v>37</v>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>RCV8843842</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D133" s="5" t="n">
-        <v>23896</v>
-      </c>
-      <c r="E133" t="s">
-        <v>42</v>
+        <v>39518</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F133" s="6" t="n">
-        <v>38.1</v>
+        <v>34.6</v>
       </c>
       <c r="G133" t="n">
         <v>4</v>
       </c>
-      <c r="H133" t="s">
-        <v>101</v>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I133" s="5" t="n">
         <v>46478</v>
@@ -5053,26 +5611,34 @@
       <c r="A134" t="n">
         <v>133</v>
       </c>
-      <c r="B134" t="s">
-        <v>178</v>
-      </c>
-      <c r="C134" t="s">
-        <v>41</v>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>RCV4985729</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D134" s="5" t="n">
-        <v>23956</v>
-      </c>
-      <c r="E134" t="s">
-        <v>42</v>
+        <v>27802</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F134" s="6" t="n">
-        <v>38.1</v>
+        <v>34.5</v>
       </c>
       <c r="G134" t="n">
         <v>4</v>
       </c>
-      <c r="H134" t="s">
-        <v>99</v>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I134" s="5" t="n">
         <v>46478</v>
@@ -5082,26 +5648,34 @@
       <c r="A135" t="n">
         <v>134</v>
       </c>
-      <c r="B135" t="s">
-        <v>179</v>
-      </c>
-      <c r="C135" t="s">
-        <v>41</v>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>RCV4088861</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D135" s="5" t="n">
-        <v>25295</v>
-      </c>
-      <c r="E135" t="s">
-        <v>42</v>
+        <v>32475</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F135" s="6" t="n">
-        <v>38</v>
+        <v>34.4</v>
       </c>
       <c r="G135" t="n">
         <v>4</v>
       </c>
-      <c r="H135" t="s">
-        <v>101</v>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I135" s="5" t="n">
         <v>46478</v>
@@ -5111,26 +5685,34 @@
       <c r="A136" t="n">
         <v>135</v>
       </c>
-      <c r="B136" t="s">
-        <v>180</v>
-      </c>
-      <c r="C136" t="s">
-        <v>37</v>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>RCV4314756</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D136" s="5" t="n">
-        <v>23473</v>
-      </c>
-      <c r="E136" t="s">
-        <v>38</v>
+        <v>30552</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F136" s="6" t="n">
-        <v>37.9</v>
+        <v>34.4</v>
       </c>
       <c r="G136" t="n">
         <v>4</v>
       </c>
-      <c r="H136" t="s">
-        <v>99</v>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I136" s="5" t="n">
         <v>46478</v>
@@ -5140,26 +5722,34 @@
       <c r="A137" t="n">
         <v>136</v>
       </c>
-      <c r="B137" t="s">
-        <v>181</v>
-      </c>
-      <c r="C137" t="s">
-        <v>58</v>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>RCV4504310</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D137" s="5" t="n">
-        <v>46292</v>
-      </c>
-      <c r="E137" t="s">
-        <v>42</v>
+        <v>25850</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F137" s="6" t="n">
-        <v>37.9</v>
+        <v>34.2</v>
       </c>
       <c r="G137" t="n">
         <v>4</v>
       </c>
-      <c r="H137" t="s">
-        <v>101</v>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I137" s="5" t="n">
         <v>46478</v>
@@ -5169,26 +5759,34 @@
       <c r="A138" t="n">
         <v>137</v>
       </c>
-      <c r="B138" t="s">
-        <v>182</v>
-      </c>
-      <c r="C138" t="s">
-        <v>41</v>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>RCV7151567</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D138" s="5" t="n">
-        <v>30220</v>
-      </c>
-      <c r="E138" t="s">
-        <v>42</v>
+        <v>35540</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F138" s="6" t="n">
-        <v>37.8</v>
+        <v>34.2</v>
       </c>
       <c r="G138" t="n">
         <v>4</v>
       </c>
-      <c r="H138" t="s">
-        <v>99</v>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I138" s="5" t="n">
         <v>46478</v>
@@ -5198,26 +5796,34 @@
       <c r="A139" t="n">
         <v>138</v>
       </c>
-      <c r="B139" t="s">
-        <v>183</v>
-      </c>
-      <c r="C139" t="s">
-        <v>37</v>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>RCV8139215</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D139" s="5" t="n">
-        <v>23964</v>
-      </c>
-      <c r="E139" t="s">
-        <v>42</v>
+        <v>22913</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F139" s="6" t="n">
-        <v>37.8</v>
+        <v>34.1</v>
       </c>
       <c r="G139" t="n">
         <v>4</v>
       </c>
-      <c r="H139" t="s">
-        <v>101</v>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Health Coach Team 2</t>
+        </is>
       </c>
       <c r="I139" s="5" t="n">
         <v>46478</v>
@@ -5227,26 +5833,34 @@
       <c r="A140" t="n">
         <v>139</v>
       </c>
-      <c r="B140" t="s">
-        <v>184</v>
-      </c>
-      <c r="C140" t="s">
-        <v>41</v>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>RCV8277482</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D140" s="5" t="n">
-        <v>28704</v>
-      </c>
-      <c r="E140" t="s">
-        <v>42</v>
+        <v>36580</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F140" s="6" t="n">
-        <v>37.7</v>
+        <v>34.1</v>
       </c>
       <c r="G140" t="n">
         <v>4</v>
       </c>
-      <c r="H140" t="s">
-        <v>99</v>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I140" s="5" t="n">
         <v>46478</v>
@@ -5256,26 +5870,34 @@
       <c r="A141" t="n">
         <v>140</v>
       </c>
-      <c r="B141" t="s">
-        <v>185</v>
-      </c>
-      <c r="C141" t="s">
-        <v>37</v>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>RCV9870490</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D141" s="5" t="n">
-        <v>24187</v>
-      </c>
-      <c r="E141" t="s">
-        <v>42</v>
+        <v>24564</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F141" s="6" t="n">
-        <v>37.7</v>
+        <v>34.1</v>
       </c>
       <c r="G141" t="n">
         <v>4</v>
       </c>
-      <c r="H141" t="s">
-        <v>101</v>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Health Coach Team 1</t>
+        </is>
       </c>
       <c r="I141" s="5" t="n">
         <v>46478</v>
@@ -5302,63 +5924,79 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>187</v>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Risk tier</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Score range</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Members</t>
+        </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>188</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>42.2 and above</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>189</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>37.9 to 42.1</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>190</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>35.7 to 37.8</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>191</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>below 35.7</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="s">
-        <v>192</v>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
       </c>
       <c r="C6" s="8" t="n">
         <v>140</v>

--- a/task130/target/northcourt_stratification_2026_claims_final.xlsx
+++ b/task130/target/northcourt_stratification_2026_claims_final.xlsx
@@ -1358,7 +1358,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RCV8692544</t>
+          <t>RCV9467205</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1367,11 +1367,11 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>24122</v>
+        <v>24582</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>RN Team C</t>
+          <t>RN Team B</t>
         </is>
       </c>
       <c r="I19" s="5" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RCV9467205</t>
+          <t>RCV7885533</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>24582</v>
+        <v>26975</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>45.7</v>
+        <v>45.5</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -1432,16 +1432,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RCV7885533</t>
+          <t>RCV4189407</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>26975</v>
+        <v>29800</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1469,16 +1469,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RCV4189407</t>
+          <t>RCV1603872</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>29800</v>
+        <v>35090</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1486,14 +1486,14 @@
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>45.5</v>
+        <v>45.3</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>RN Team B</t>
+          <t>RN Team C</t>
         </is>
       </c>
       <c r="I22" s="5" t="n">
@@ -1506,31 +1506,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RCV1603872</t>
+          <t>RCV9255613</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>35090</v>
+        <v>26377</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>45.3</v>
+        <v>44.8</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>RN Team C</t>
+          <t>RN Team A</t>
         </is>
       </c>
       <c r="I23" s="5" t="n">
@@ -1543,20 +1543,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RCV9255613</t>
+          <t>RCV6227172</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Dependent</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>26377</v>
+        <v>42371</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>RN Team A</t>
+          <t>RN Team C</t>
         </is>
       </c>
       <c r="I24" s="5" t="n">
@@ -1580,16 +1580,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RCV6227172</t>
+          <t>RCV2751065</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dependent</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>42371</v>
+        <v>24692</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1597,14 +1597,14 @@
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>44.8</v>
+        <v>44.5</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>RN Team C</t>
+          <t>RN Team A</t>
         </is>
       </c>
       <c r="I25" s="5" t="n">
@@ -1617,16 +1617,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RCV2751065</t>
+          <t>RCV3082787</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>24692</v>
+        <v>27148</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>44.5</v>
+        <v>43.8</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -1654,31 +1654,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RCV3082787</t>
+          <t>RCV5995844</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>27148</v>
+        <v>21605</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>RN Team A</t>
+          <t>RN Team C</t>
         </is>
       </c>
       <c r="I27" s="5" t="n">
@@ -1691,31 +1691,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RCV5995844</t>
+          <t>RCV4587185</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>21605</v>
+        <v>24894</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>RN Team C</t>
+          <t>RN Team B</t>
         </is>
       </c>
       <c r="I28" s="5" t="n">
@@ -1728,31 +1728,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RCV4587185</t>
+          <t>RCV9304806</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>24894</v>
+        <v>24622</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>43.6</v>
+        <v>43.1</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>RN Team B</t>
+          <t>RN Team C</t>
         </is>
       </c>
       <c r="I29" s="5" t="n">
@@ -1765,24 +1765,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RCV9304806</t>
+          <t>RCV8608275</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>24622</v>
+        <v>31641</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RCV8608275</t>
+          <t>RCV8509472</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>31641</v>
+        <v>27468</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1819,14 +1819,14 @@
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>43</v>
+        <v>42.7</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>RN Team C</t>
+          <t>RN Team B</t>
         </is>
       </c>
       <c r="I31" s="5" t="n">
@@ -1839,16 +1839,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RCV8509472</t>
+          <t>RCV7426097</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Dependent</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>27468</v>
+        <v>46345</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>RN Team B</t>
+          <t>RN Team C</t>
         </is>
       </c>
       <c r="I32" s="5" t="n">
@@ -1876,20 +1876,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RCV7426097</t>
+          <t>RCV1049263</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dependent</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>46345</v>
+        <v>32024</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>RN Team C</t>
+          <t>RN Team B</t>
         </is>
       </c>
       <c r="I33" s="5" t="n">
@@ -1913,16 +1913,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RCV1049263</t>
+          <t>RCV7157512</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>32024</v>
+        <v>23754</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>RN Team B</t>
+          <t>RN Team C</t>
         </is>
       </c>
       <c r="I34" s="5" t="n">
@@ -1950,16 +1950,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RCV7157512</t>
+          <t>RCV6938522</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>23754</v>
+        <v>25222</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1967,14 +1967,14 @@
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>42.7</v>
+        <v>42.3</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>RN Team C</t>
+          <t>RN Team A</t>
         </is>
       </c>
       <c r="I35" s="5" t="n">
@@ -1987,31 +1987,31 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RCV6938522</t>
+          <t>RCV4201512</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>25222</v>
+        <v>29300</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>42.3</v>
+        <v>42</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>RN Team A</t>
+          <t>RN Team C</t>
         </is>
       </c>
       <c r="I36" s="5" t="n">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RCV4201512</t>
+          <t>RCV1855123</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>29300</v>
+        <v>32038</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>42</v>
+        <v>41.5</v>
       </c>
       <c r="G37" t="n">
         <v>2</v>
@@ -2061,31 +2061,31 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RCV1855123</t>
+          <t>RCV3713263</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>32038</v>
+        <v>29087</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="G38" t="n">
         <v>2</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>RN Team C</t>
+          <t>RN Team B</t>
         </is>
       </c>
       <c r="I38" s="5" t="n">
@@ -2098,20 +2098,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RCV3713263</t>
+          <t>RCV5579448</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>29087</v>
+        <v>25764</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>RN Team B</t>
+          <t>RN Team C</t>
         </is>
       </c>
       <c r="I39" s="5" t="n">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RCV5579448</t>
+          <t>RCV5181969</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2144,22 +2144,22 @@
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>25764</v>
+        <v>23566</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>41.4</v>
+        <v>40.9</v>
       </c>
       <c r="G40" t="n">
         <v>2</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>RN Team C</t>
+          <t>RN Team A</t>
         </is>
       </c>
       <c r="I40" s="5" t="n">
@@ -2172,16 +2172,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RCV5181969</t>
+          <t>RCV5078746</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>23566</v>
+        <v>28655</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>RN Team A</t>
+          <t>RN Team B</t>
         </is>
       </c>
       <c r="I41" s="5" t="n">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RCV5078746</t>
+          <t>RCV5824630</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2218,22 +2218,22 @@
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>28655</v>
+        <v>28492</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="G42" t="n">
         <v>2</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>RN Team B</t>
+          <t>RN Team A</t>
         </is>
       </c>
       <c r="I42" s="5" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RCV5824630</t>
+          <t>RCV1070060</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2255,11 +2255,11 @@
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>28492</v>
+        <v>30349</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>RN Team A</t>
+          <t>RN Team C</t>
         </is>
       </c>
       <c r="I43" s="5" t="n">
@@ -2283,16 +2283,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RCV1070060</t>
+          <t>RCV6875151</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Dependent</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>30349</v>
+        <v>40112</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2320,20 +2320,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RCV6875151</t>
+          <t>RCV2327923</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dependent</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>40112</v>
+        <v>25183</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>RN Team C</t>
+          <t>RN Team B</t>
         </is>
       </c>
       <c r="I45" s="5" t="n">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RCV2327923</t>
+          <t>RCV6795042</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2366,11 +2366,11 @@
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>25183</v>
+        <v>23652</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
@@ -2394,31 +2394,31 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RCV6795042</t>
+          <t>RCV8852933</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>23652</v>
+        <v>26254</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>40.8</v>
+        <v>40.6</v>
       </c>
       <c r="G47" t="n">
         <v>2</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>RN Team B</t>
+          <t>RN Team C</t>
         </is>
       </c>
       <c r="I47" s="5" t="n">
@@ -2431,16 +2431,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RCV8852933</t>
+          <t>RCV2365593</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>26254</v>
+        <v>33612</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>40.6</v>
+        <v>40.4</v>
       </c>
       <c r="G48" t="n">
         <v>2</v>
@@ -2468,24 +2468,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RCV2365593</t>
+          <t>RCV3282444</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>33612</v>
+        <v>34034</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>40.4</v>
+        <v>40.1</v>
       </c>
       <c r="G49" t="n">
         <v>2</v>
@@ -2505,31 +2505,31 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RCV3282444</t>
+          <t>RCV8050854</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>34034</v>
+        <v>24862</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>40.1</v>
+        <v>40</v>
       </c>
       <c r="G50" t="n">
         <v>2</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>RN Team C</t>
+          <t>RN Team B</t>
         </is>
       </c>
       <c r="I50" s="5" t="n">
@@ -2542,16 +2542,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RCV8050854</t>
+          <t>RCV2919565</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>24862</v>
+        <v>24306</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>40</v>
+        <v>39.7</v>
       </c>
       <c r="G51" t="n">
         <v>2</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>RN Team B</t>
+          <t>RN Team C</t>
         </is>
       </c>
       <c r="I51" s="5" t="n">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RCV2919565</t>
+          <t>RCV5510200</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2588,7 +2588,7 @@
         </is>
       </c>
       <c r="D52" s="5" t="n">
-        <v>24306</v>
+        <v>28439</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2596,14 +2596,14 @@
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>39.7</v>
+        <v>39.4</v>
       </c>
       <c r="G52" t="n">
         <v>2</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>RN Team C</t>
+          <t>RN Team B</t>
         </is>
       </c>
       <c r="I52" s="5" t="n">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RCV5510200</t>
+          <t>RCV5168987</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>28439</v>
+        <v>33637</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2633,14 +2633,14 @@
         </is>
       </c>
       <c r="F53" s="6" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="G53" t="n">
         <v>2</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>RN Team B</t>
+          <t>RN Team C</t>
         </is>
       </c>
       <c r="I53" s="5" t="n">
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RCV5168987</t>
+          <t>RCV5566499</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Dependent</t>
         </is>
       </c>
       <c r="D54" s="5" t="n">
-        <v>33637</v>
+        <v>46134</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F54" s="6" t="n">
@@ -2690,31 +2690,31 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RCV5566499</t>
+          <t>RCV4899050</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dependent</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>46134</v>
+        <v>24208</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
-        <v>39.3</v>
+        <v>39.1</v>
       </c>
       <c r="G55" t="n">
         <v>2</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>RN Team C</t>
+          <t>RN Team A</t>
         </is>
       </c>
       <c r="I55" s="5" t="n">
@@ -2727,20 +2727,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RCV4899050</t>
+          <t>RCV1947586</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D56" s="5" t="n">
-        <v>24208</v>
+        <v>35326</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F56" s="6" t="n">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>RN Team A</t>
+          <t>RN Team C</t>
         </is>
       </c>
       <c r="I56" s="5" t="n">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RCV1947586</t>
+          <t>RCV5863375</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>35326</v>
+        <v>20965</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2781,14 +2781,14 @@
         </is>
       </c>
       <c r="F57" s="6" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="G57" t="n">
         <v>2</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>RN Team C</t>
+          <t>RN Team A</t>
         </is>
       </c>
       <c r="I57" s="5" t="n">
@@ -2801,20 +2801,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RCV5863375</t>
+          <t>RCV1203862</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D58" s="5" t="n">
-        <v>20965</v>
+        <v>30841</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F58" s="6" t="n">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>RN Team A</t>
+          <t>RN Team C</t>
         </is>
       </c>
       <c r="I58" s="5" t="n">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RCV1203862</t>
+          <t>RCV8834952</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>30841</v>
+        <v>35129</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F59" s="6" t="n">
-        <v>39</v>
+        <v>38.7</v>
       </c>
       <c r="G59" t="n">
         <v>2</v>
@@ -2875,20 +2875,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RCV8834952</t>
+          <t>RCV2810335</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D60" s="5" t="n">
-        <v>35129</v>
+        <v>25295</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F60" s="6" t="n">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>RN Team C</t>
+          <t>RN Team B</t>
         </is>
       </c>
       <c r="I60" s="5" t="n">
@@ -2912,20 +2912,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RCV2810335</t>
+          <t>RCV4951271</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>25295</v>
+        <v>27969</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F61" s="6" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>RN Team B</t>
+          <t>RN Team C</t>
         </is>
       </c>
       <c r="I61" s="5" t="n">
@@ -2949,24 +2949,24 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RCV4951271</t>
+          <t>RCV7668760</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Dependent</t>
         </is>
       </c>
       <c r="D62" s="5" t="n">
-        <v>27969</v>
+        <v>37190</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F62" s="6" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="G62" t="n">
         <v>2</v>
@@ -2986,24 +2986,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RCV7668760</t>
+          <t>RCV9968668</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dependent</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>37190</v>
+        <v>32548</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F63" s="6" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="G63" t="n">
         <v>2</v>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RCV9968668</t>
+          <t>RCV6032188</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>32548</v>
+        <v>30936</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -3060,16 +3060,16 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RCV6032188</t>
+          <t>RCV1657905</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>30936</v>
+        <v>30867</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="F65" s="6" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="G65" t="n">
         <v>2</v>
@@ -3097,16 +3097,16 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RCV1657905</t>
+          <t>RCV3942326</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D66" s="5" t="n">
-        <v>30867</v>
+        <v>27790</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>RN Team C</t>
+          <t>RN Team B</t>
         </is>
       </c>
       <c r="I66" s="5" t="n">
@@ -3134,31 +3134,31 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RCV3942326</t>
+          <t>RCV4533275</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Dependent</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>27790</v>
+        <v>46224</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F67" s="6" t="n">
-        <v>38.4</v>
+        <v>38.1</v>
       </c>
       <c r="G67" t="n">
         <v>2</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>RN Team B</t>
+          <t>RN Team C</t>
         </is>
       </c>
       <c r="I67" s="5" t="n">
@@ -3171,16 +3171,16 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RCV4533275</t>
+          <t>RCV1315676</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dependent</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D68" s="5" t="n">
-        <v>46224</v>
+        <v>27786</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         </is>
       </c>
       <c r="F68" s="6" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="G68" t="n">
         <v>2</v>
@@ -3208,16 +3208,16 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RCV1315676</t>
+          <t>RCV5283668</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>27786</v>
+        <v>28947</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RCV5283668</t>
+          <t>RCV5315428</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="D70" s="5" t="n">
-        <v>28947</v>
+        <v>30154</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         </is>
       </c>
       <c r="F70" s="6" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="G70" t="n">
         <v>2</v>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RCV5315428</t>
+          <t>RCV9495454</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3291,11 +3291,11 @@
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>30154</v>
+        <v>28824</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F71" s="6" t="n">
@@ -3319,16 +3319,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RCV9495454</t>
+          <t>RCV2960214</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>28824</v>
+        <v>27298</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>RCV2960214</t>
+          <t>RCV2409617</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>27298</v>
+        <v>28877</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3373,14 +3373,14 @@
         </is>
       </c>
       <c r="F73" s="6" t="n">
-        <v>37.9</v>
+        <v>37.7</v>
       </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>RN Team C</t>
+          <t>Health Coach Team 1</t>
         </is>
       </c>
       <c r="I73" s="5" t="n">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RCV2409617</t>
+          <t>RCV3340479</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3402,22 +3402,22 @@
         </is>
       </c>
       <c r="D74" s="5" t="n">
-        <v>28877</v>
+        <v>33533</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F74" s="6" t="n">
-        <v>37.7</v>
+        <v>37.5</v>
       </c>
       <c r="G74" t="n">
         <v>3</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Health Coach Team 1</t>
+          <t>Health Coach Team 2</t>
         </is>
       </c>
       <c r="I74" s="5" t="n">
@@ -3430,16 +3430,16 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RCV3340479</t>
+          <t>RCV4210913</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Dependent</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>33533</v>
+        <v>37516</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Health Coach Team 2</t>
+          <t>Health Coach Team 1</t>
         </is>
       </c>
       <c r="I75" s="5" t="n">
@@ -3467,24 +3467,24 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RCV4210913</t>
+          <t>RCV1277465</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dependent</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D76" s="5" t="n">
-        <v>37516</v>
+        <v>27961</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="G76" t="n">
         <v>3</v>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RCV1277465</t>
+          <t>RCV5591867</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="D77" s="5" t="n">
-        <v>27961</v>
+        <v>27813</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="F77" s="6" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="G77" t="n">
         <v>3</v>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RCV5591867</t>
+          <t>RCV7862809</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="D78" s="5" t="n">
-        <v>27813</v>
+        <v>31271</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RCV7862809</t>
+          <t>RCV8014223</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3587,15 +3587,15 @@
         </is>
       </c>
       <c r="D79" s="5" t="n">
-        <v>31271</v>
+        <v>27902</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F79" s="6" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="G79" t="n">
         <v>3</v>
@@ -3615,16 +3615,16 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>RCV8014223</t>
+          <t>RCV7061717</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Dependent</t>
         </is>
       </c>
       <c r="D80" s="5" t="n">
-        <v>27902</v>
+        <v>43283</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>RCV7061717</t>
+          <t>RCV4467829</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3661,11 +3661,11 @@
         </is>
       </c>
       <c r="D81" s="5" t="n">
-        <v>43283</v>
+        <v>37122</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F81" s="6" t="n">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Health Coach Team 1</t>
+          <t>Health Coach Team 2</t>
         </is>
       </c>
       <c r="I81" s="5" t="n">
@@ -3689,20 +3689,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>RCV4467829</t>
+          <t>RCV9437872</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dependent</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D82" s="5" t="n">
-        <v>37122</v>
+        <v>29427</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F82" s="6" t="n">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Health Coach Team 2</t>
+          <t>Health Coach Team 1</t>
         </is>
       </c>
       <c r="I82" s="5" t="n">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>RCV9437872</t>
+          <t>RCV5279940</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="D83" s="5" t="n">
-        <v>29427</v>
+        <v>23734</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="F83" s="6" t="n">
-        <v>37.1</v>
+        <v>36.9</v>
       </c>
       <c r="G83" t="n">
         <v>3</v>
@@ -3763,16 +3763,16 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>RCV5279940</t>
+          <t>RCV1937360</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D84" s="5" t="n">
-        <v>23734</v>
+        <v>33054</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>RCV1937360</t>
+          <t>RCV9952179</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3809,11 +3809,11 @@
         </is>
       </c>
       <c r="D85" s="5" t="n">
-        <v>33054</v>
+        <v>26412</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F85" s="6" t="n">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>RCV9952179</t>
+          <t>RCV2975871</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3846,7 +3846,7 @@
         </is>
       </c>
       <c r="D86" s="5" t="n">
-        <v>26412</v>
+        <v>29352</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F86" s="6" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="G86" t="n">
         <v>3</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>RCV2975871</t>
+          <t>RCV8621093</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3883,15 +3883,15 @@
         </is>
       </c>
       <c r="D87" s="5" t="n">
-        <v>29352</v>
+        <v>31277</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F87" s="6" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="G87" t="n">
         <v>3</v>
@@ -3911,16 +3911,16 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>RCV8621093</t>
+          <t>RCV6197369</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D88" s="5" t="n">
-        <v>31277</v>
+        <v>35840</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="F88" s="6" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="G88" t="n">
         <v>3</v>
@@ -3948,16 +3948,16 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>RCV6197369</t>
+          <t>RCV1523489</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D89" s="5" t="n">
-        <v>35840</v>
+        <v>24655</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>RCV1523489</t>
+          <t>RCV5710113</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3994,22 +3994,22 @@
         </is>
       </c>
       <c r="D90" s="5" t="n">
-        <v>24655</v>
+        <v>26352</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F90" s="6" t="n">
-        <v>36.6</v>
+        <v>36.4</v>
       </c>
       <c r="G90" t="n">
         <v>3</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Health Coach Team 1</t>
+          <t>Health Coach Team 2</t>
         </is>
       </c>
       <c r="I90" s="5" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>RCV5710113</t>
+          <t>RCV7304462</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="D91" s="5" t="n">
-        <v>26352</v>
+        <v>25208</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -4039,14 +4039,14 @@
         </is>
       </c>
       <c r="F91" s="6" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="G91" t="n">
         <v>3</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Health Coach Team 2</t>
+          <t>Health Coach Team 1</t>
         </is>
       </c>
       <c r="I91" s="5" t="n">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>RCV7304462</t>
+          <t>RCV3448604</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="D92" s="5" t="n">
-        <v>25208</v>
+        <v>32216</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -4096,16 +4096,16 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>RCV3448604</t>
+          <t>RCV5746488</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Dependent</t>
         </is>
       </c>
       <c r="D93" s="5" t="n">
-        <v>32216</v>
+        <v>46315</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Health Coach Team 1</t>
+          <t>Health Coach Team 2</t>
         </is>
       </c>
       <c r="I93" s="5" t="n">
@@ -4133,16 +4133,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>RCV5746488</t>
+          <t>RCV2632014</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dependent</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D94" s="5" t="n">
-        <v>46315</v>
+        <v>23907</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -4170,16 +4170,16 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>RCV2632014</t>
+          <t>RCV6769341</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D95" s="5" t="n">
-        <v>23907</v>
+        <v>24072</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Health Coach Team 2</t>
+          <t>Health Coach Team 1</t>
         </is>
       </c>
       <c r="I95" s="5" t="n">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>RCV6769341</t>
+          <t>RCV3217981</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="D96" s="5" t="n">
-        <v>24072</v>
+        <v>28198</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         </is>
       </c>
       <c r="F96" s="6" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="G96" t="n">
         <v>3</v>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>RCV3217981</t>
+          <t>RCV2747077</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="D97" s="5" t="n">
-        <v>28198</v>
+        <v>28998</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Health Coach Team 1</t>
+          <t>Health Coach Team 2</t>
         </is>
       </c>
       <c r="I97" s="5" t="n">
@@ -4281,24 +4281,24 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>RCV2747077</t>
+          <t>RCV9766459</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D98" s="5" t="n">
-        <v>28998</v>
+        <v>24804</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F98" s="6" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="G98" t="n">
         <v>3</v>
@@ -4318,20 +4318,20 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>RCV9766459</t>
+          <t>RCV6190692</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
-        <v>24804</v>
+        <v>30533</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F99" s="6" t="n">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Health Coach Team 2</t>
+          <t>Health Coach Team 1</t>
         </is>
       </c>
       <c r="I99" s="5" t="n">
@@ -4355,31 +4355,31 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>RCV6190692</t>
+          <t>RCV4869334</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D100" s="5" t="n">
-        <v>30533</v>
+        <v>26404</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F100" s="6" t="n">
-        <v>36.1</v>
+        <v>35.9</v>
       </c>
       <c r="G100" t="n">
         <v>3</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Health Coach Team 1</t>
+          <t>Health Coach Team 2</t>
         </is>
       </c>
       <c r="I100" s="5" t="n">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>RCV4869334</t>
+          <t>RCV7845029</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>26404</v>
+        <v>26342</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -4429,20 +4429,20 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>RCV7845029</t>
+          <t>RCV1071872</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D102" s="5" t="n">
-        <v>26342</v>
+        <v>26578</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F102" s="6" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>RCV1071872</t>
+          <t>RCV1913391</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="D103" s="5" t="n">
-        <v>26578</v>
+        <v>27834</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Health Coach Team 2</t>
+          <t>Health Coach Team 1</t>
         </is>
       </c>
       <c r="I103" s="5" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>RCV1913391</t>
+          <t>RCV9121410</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4512,7 +4512,7 @@
         </is>
       </c>
       <c r="D104" s="5" t="n">
-        <v>27834</v>
+        <v>28952</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Health Coach Team 1</t>
+          <t>Health Coach Team 2</t>
         </is>
       </c>
       <c r="I104" s="5" t="n">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>RCV9121410</t>
+          <t>RCV6528527</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4549,7 +4549,7 @@
         </is>
       </c>
       <c r="D105" s="5" t="n">
-        <v>28952</v>
+        <v>23942</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="F105" s="6" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="G105" t="n">
         <v>3</v>
@@ -4577,7 +4577,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>RCV6528527</t>
+          <t>RCV5515162</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4586,11 +4586,11 @@
         </is>
       </c>
       <c r="D106" s="5" t="n">
-        <v>23942</v>
+        <v>24710</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F106" s="6" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Health Coach Team 2</t>
+          <t>Health Coach Team 1</t>
         </is>
       </c>
       <c r="I106" s="5" t="n">
@@ -4614,16 +4614,16 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>RCV5515162</t>
+          <t>RCV9868322</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
-        <v>24710</v>
+        <v>29832</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Health Coach Team 1</t>
+          <t>Health Coach Team 2</t>
         </is>
       </c>
       <c r="I107" s="5" t="n">
@@ -4651,24 +4651,24 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>RCV9868322</t>
+          <t>RCV2747974</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D108" s="5" t="n">
-        <v>29832</v>
+        <v>23888</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F108" s="6" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="G108" t="n">
         <v>3</v>
@@ -4688,7 +4688,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>RCV2747974</t>
+          <t>RCV8318861</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="D109" s="5" t="n">
-        <v>23888</v>
+        <v>24802</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Health Coach Team 2</t>
+          <t>Health Coach Team 1</t>
         </is>
       </c>
       <c r="I109" s="5" t="n">
@@ -4725,20 +4725,20 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>RCV8318861</t>
+          <t>RCV6796246</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Dependent</t>
         </is>
       </c>
       <c r="D110" s="5" t="n">
-        <v>24802</v>
+        <v>37581</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F110" s="6" t="n">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Health Coach Team 1</t>
+          <t>Health Coach Team 2</t>
         </is>
       </c>
       <c r="I110" s="5" t="n">
@@ -4762,31 +4762,31 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>RCV6796246</t>
+          <t>RCV5346787</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Dependent</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
-        <v>37581</v>
+        <v>24109</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F111" s="6" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="G111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Health Coach Team 2</t>
+          <t>Health Coach Team 1</t>
         </is>
       </c>
       <c r="I111" s="5" t="n">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>RCV5346787</t>
+          <t>RCV2283246</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4808,7 +4808,7 @@
         </is>
       </c>
       <c r="D112" s="5" t="n">
-        <v>24109</v>
+        <v>25235</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="F112" s="6" t="n">
-        <v>35.6</v>
+        <v>35.4</v>
       </c>
       <c r="G112" t="n">
         <v>4</v>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>RCV2283246</t>
+          <t>RCV5202951</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4845,11 +4845,11 @@
         </is>
       </c>
       <c r="D113" s="5" t="n">
-        <v>25235</v>
+        <v>26983</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F113" s="6" t="n">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Health Coach Team 1</t>
+          <t>Health Coach Team 2</t>
         </is>
       </c>
       <c r="I113" s="5" t="n">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>RCV5202951</t>
+          <t>RCV5380081</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4882,22 +4882,22 @@
         </is>
       </c>
       <c r="D114" s="5" t="n">
-        <v>26983</v>
+        <v>30367</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F114" s="6" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="G114" t="n">
         <v>4</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Health Coach Team 2</t>
+          <t>Health Coach Team 1</t>
         </is>
       </c>
       <c r="I114" s="5" t="n">
@@ -4910,20 +4910,20 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>RCV5380081</t>
+          <t>RCV9761816</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
-        <v>30367</v>
+        <v>33923</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F115" s="6" t="n">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Health Coach Team 1</t>
+          <t>Health Coach Team 2</t>
         </is>
       </c>
       <c r="I115" s="5" t="n">
@@ -4947,24 +4947,24 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>RCV9761816</t>
+          <t>RCV4711403</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D116" s="5" t="n">
-        <v>33923</v>
+        <v>30268</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F116" s="6" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="G116" t="n">
         <v>4</v>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>RCV4711403</t>
+          <t>RCV3189078</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="D117" s="5" t="n">
-        <v>30268</v>
+        <v>26567</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>RCV3189078</t>
+          <t>RCV4756035</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="D118" s="5" t="n">
-        <v>26567</v>
+        <v>32179</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Health Coach Team 2</t>
+          <t>Health Coach Team 1</t>
         </is>
       </c>
       <c r="I118" s="5" t="n">
@@ -5058,16 +5058,16 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>RCV4756035</t>
+          <t>RCV1123220</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Dependent</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
-        <v>32179</v>
+        <v>40929</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -5095,16 +5095,16 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>RCV1123220</t>
+          <t>RCV5866544</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Dependent</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D120" s="5" t="n">
-        <v>40929</v>
+        <v>26442</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -5112,14 +5112,14 @@
         </is>
       </c>
       <c r="F120" s="6" t="n">
-        <v>35.2</v>
+        <v>35</v>
       </c>
       <c r="G120" t="n">
         <v>4</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Health Coach Team 1</t>
+          <t>Health Coach Team 2</t>
         </is>
       </c>
       <c r="I120" s="5" t="n">
@@ -5132,16 +5132,16 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>RCV5866544</t>
+          <t>RCV4268380</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Dependent</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
-        <v>26442</v>
+        <v>46273</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Health Coach Team 2</t>
+          <t>Health Coach Team 1</t>
         </is>
       </c>
       <c r="I121" s="5" t="n">
@@ -5169,16 +5169,16 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>RCV4268380</t>
+          <t>RCV9596296</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Dependent</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D122" s="5" t="n">
-        <v>46273</v>
+        <v>35110</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="F122" s="6" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="G122" t="n">
         <v>4</v>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>RCV9596296</t>
+          <t>RCV7028261</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="D123" s="5" t="n">
-        <v>35110</v>
+        <v>33353</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -5223,14 +5223,14 @@
         </is>
       </c>
       <c r="F123" s="6" t="n">
-        <v>34.9</v>
+        <v>34.8</v>
       </c>
       <c r="G123" t="n">
         <v>4</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Health Coach Team 1</t>
+          <t>Health Coach Team 2</t>
         </is>
       </c>
       <c r="I123" s="5" t="n">
@@ -5243,20 +5243,20 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>RCV7028261</t>
+          <t>RCV3651381</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D124" s="5" t="n">
-        <v>33353</v>
+        <v>22917</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F124" s="6" t="n">
@@ -5280,16 +5280,16 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>RCV3651381</t>
+          <t>RCV5755390</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
-        <v>22917</v>
+        <v>26511</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Health Coach Team 2</t>
+          <t>Health Coach Team 1</t>
         </is>
       </c>
       <c r="I125" s="5" t="n">
@@ -5317,24 +5317,24 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>RCV5755390</t>
+          <t>RCV7948468</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D126" s="5" t="n">
-        <v>26511</v>
+        <v>30313</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F126" s="6" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
       <c r="G126" t="n">
         <v>4</v>
@@ -5354,20 +5354,20 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>RCV7948468</t>
+          <t>RCV2102741</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
-        <v>30313</v>
+        <v>24658</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F127" s="6" t="n">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Health Coach Team 1</t>
+          <t>Health Coach Team 2</t>
         </is>
       </c>
       <c r="I127" s="5" t="n">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>RCV2102741</t>
+          <t>RCV4477427</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5400,11 +5400,11 @@
         </is>
       </c>
       <c r="D128" s="5" t="n">
-        <v>24658</v>
+        <v>26813</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F128" s="6" t="n">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>RCV4477427</t>
+          <t>RCV8733567</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5437,22 +5437,22 @@
         </is>
       </c>
       <c r="D129" s="5" t="n">
-        <v>26813</v>
+        <v>29775</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F129" s="6" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="G129" t="n">
         <v>4</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Health Coach Team 2</t>
+          <t>Health Coach Team 1</t>
         </is>
       </c>
       <c r="I129" s="5" t="n">
@@ -5465,16 +5465,16 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>RCV8733567</t>
+          <t>RCV1589842</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D130" s="5" t="n">
-        <v>29775</v>
+        <v>25677</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -5502,16 +5502,16 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>RCV1589842</t>
+          <t>RCV8057849</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
-        <v>25677</v>
+        <v>25491</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Health Coach Team 1</t>
+          <t>Health Coach Team 2</t>
         </is>
       </c>
       <c r="I131" s="5" t="n">
@@ -5539,16 +5539,16 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>RCV8057849</t>
+          <t>RCV8843842</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Dependent</t>
         </is>
       </c>
       <c r="D132" s="5" t="n">
-        <v>25491</v>
+        <v>39518</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -5576,16 +5576,16 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>RCV8843842</t>
+          <t>RCV4985729</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Dependent</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
-        <v>39518</v>
+        <v>27802</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="F133" s="6" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="G133" t="n">
         <v>4</v>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>RCV4985729</t>
+          <t>RCV4088861</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5622,22 +5622,22 @@
         </is>
       </c>
       <c r="D134" s="5" t="n">
-        <v>27802</v>
+        <v>32475</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F134" s="6" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="G134" t="n">
         <v>4</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Health Coach Team 2</t>
+          <t>Health Coach Team 1</t>
         </is>
       </c>
       <c r="I134" s="5" t="n">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>RCV4088861</t>
+          <t>RCV4314756</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5659,11 +5659,11 @@
         </is>
       </c>
       <c r="D135" s="5" t="n">
-        <v>32475</v>
+        <v>30552</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F135" s="6" t="n">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>RCV4314756</t>
+          <t>RCV4504310</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="D136" s="5" t="n">
-        <v>30552</v>
+        <v>25850</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         </is>
       </c>
       <c r="F136" s="6" t="n">
-        <v>34.4</v>
+        <v>34.2</v>
       </c>
       <c r="G136" t="n">
         <v>4</v>
@@ -5724,20 +5724,20 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>RCV4504310</t>
+          <t>RCV7151567</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
-        <v>25850</v>
+        <v>35540</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F137" s="6" t="n">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Health Coach Team 1</t>
+          <t>Health Coach Team 2</t>
         </is>
       </c>
       <c r="I137" s="5" t="n">
@@ -5761,24 +5761,24 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>RCV7151567</t>
+          <t>RCV8139215</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D138" s="5" t="n">
-        <v>35540</v>
+        <v>22913</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F138" s="6" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="G138" t="n">
         <v>4</v>
@@ -5798,20 +5798,20 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>RCV8139215</t>
+          <t>RCV8277482</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
-        <v>22913</v>
+        <v>36580</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F139" s="6" t="n">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Health Coach Team 2</t>
+          <t>Health Coach Team 1</t>
         </is>
       </c>
       <c r="I139" s="5" t="n">
@@ -5835,20 +5835,20 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>RCV8277482</t>
+          <t>RCV9870490</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Subscriber</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="D140" s="5" t="n">
-        <v>36580</v>
+        <v>24564</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F140" s="6" t="n">
@@ -5872,20 +5872,20 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>RCV9870490</t>
+          <t>RCV9058604</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Subscriber</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
-        <v>24564</v>
+        <v>31045</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F141" s="6" t="n">
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
